--- a/data/demo_assets/sensor_readings.xlsx
+++ b/data/demo_assets/sensor_readings.xlsx
@@ -455,10 +455,10 @@
         <v>46266.33333333334</v>
       </c>
       <c r="B3" t="n">
-        <v>108.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>428.4</v>
+        <v>414.4</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         <v>46266.33402777778</v>
       </c>
       <c r="B4" t="n">
-        <v>104.4</v>
+        <v>107.6</v>
       </c>
       <c r="C4" t="n">
-        <v>410.6</v>
+        <v>424.2</v>
       </c>
     </row>
     <row r="5">
@@ -477,10 +477,10 @@
         <v>46266.33472222222</v>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>444.2</v>
+        <v>431.5</v>
       </c>
     </row>
     <row r="6">
@@ -488,10 +488,10 @@
         <v>46266.33541666667</v>
       </c>
       <c r="B6" t="n">
-        <v>102.9</v>
+        <v>106</v>
       </c>
       <c r="C6" t="n">
-        <v>407.1</v>
+        <v>435.5</v>
       </c>
     </row>
     <row r="7">
@@ -499,10 +499,10 @@
         <v>46266.33611111111</v>
       </c>
       <c r="B7" t="n">
-        <v>92.8</v>
+        <v>96.2</v>
       </c>
       <c r="C7" t="n">
-        <v>437.2</v>
+        <v>400.7</v>
       </c>
     </row>
     <row r="8">
@@ -510,10 +510,10 @@
         <v>46266.33680555555</v>
       </c>
       <c r="B8" t="n">
-        <v>100.8</v>
+        <v>98.2</v>
       </c>
       <c r="C8" t="n">
-        <v>437.4</v>
+        <v>411.2</v>
       </c>
     </row>
     <row r="9">
@@ -521,10 +521,10 @@
         <v>46266.3375</v>
       </c>
       <c r="B9" t="n">
-        <v>98.59999999999999</v>
+        <v>106.8</v>
       </c>
       <c r="C9" t="n">
-        <v>429.2</v>
+        <v>405.7</v>
       </c>
     </row>
     <row r="10">
@@ -532,10 +532,10 @@
         <v>46266.33819444444</v>
       </c>
       <c r="B10" t="n">
-        <v>97.2</v>
+        <v>108.9</v>
       </c>
       <c r="C10" t="n">
-        <v>449.9</v>
+        <v>432.4</v>
       </c>
     </row>
     <row r="11">
@@ -543,10 +543,10 @@
         <v>46266.33888888889</v>
       </c>
       <c r="B11" t="n">
-        <v>92.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>424.7</v>
+        <v>446.6</v>
       </c>
     </row>
     <row r="12">
@@ -554,10 +554,10 @@
         <v>46266.33958333333</v>
       </c>
       <c r="B12" t="n">
-        <v>105.1</v>
+        <v>95.8</v>
       </c>
       <c r="C12" t="n">
-        <v>443.1</v>
+        <v>435.3</v>
       </c>
     </row>
     <row r="13">
@@ -565,10 +565,10 @@
         <v>46266.34027777778</v>
       </c>
       <c r="B13" t="n">
-        <v>93.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="C13" t="n">
-        <v>408</v>
+        <v>424.1</v>
       </c>
     </row>
     <row r="14">
@@ -576,10 +576,10 @@
         <v>46266.34097222222</v>
       </c>
       <c r="B14" t="n">
-        <v>103.6</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>429.8</v>
+        <v>422.8</v>
       </c>
     </row>
     <row r="15">
@@ -587,10 +587,10 @@
         <v>46266.34166666667</v>
       </c>
       <c r="B15" t="n">
-        <v>97.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>429.8</v>
+        <v>409.5</v>
       </c>
     </row>
     <row r="16">
@@ -598,10 +598,10 @@
         <v>46266.34236111111</v>
       </c>
       <c r="B16" t="n">
-        <v>99.40000000000001</v>
+        <v>102</v>
       </c>
       <c r="C16" t="n">
-        <v>412.6</v>
+        <v>437.3</v>
       </c>
     </row>
     <row r="17">
@@ -609,10 +609,10 @@
         <v>46266.34305555555</v>
       </c>
       <c r="B17" t="n">
-        <v>101.1</v>
+        <v>92.7</v>
       </c>
       <c r="C17" t="n">
-        <v>447.1</v>
+        <v>403.5</v>
       </c>
     </row>
     <row r="18">
@@ -620,10 +620,10 @@
         <v>46266.34375</v>
       </c>
       <c r="B18" t="n">
-        <v>103.6</v>
+        <v>105.5</v>
       </c>
       <c r="C18" t="n">
-        <v>405.7</v>
+        <v>442.7</v>
       </c>
     </row>
     <row r="19">
@@ -631,10 +631,10 @@
         <v>46266.34444444445</v>
       </c>
       <c r="B19" t="n">
-        <v>107.7</v>
+        <v>96.8</v>
       </c>
       <c r="C19" t="n">
-        <v>437.5</v>
+        <v>439.4</v>
       </c>
     </row>
     <row r="20">
@@ -642,10 +642,10 @@
         <v>46266.34513888889</v>
       </c>
       <c r="B20" t="n">
-        <v>105.4</v>
+        <v>95.3</v>
       </c>
       <c r="C20" t="n">
-        <v>417</v>
+        <v>400.1</v>
       </c>
     </row>
     <row r="21">
@@ -653,10 +653,10 @@
         <v>46266.34583333333</v>
       </c>
       <c r="B21" t="n">
-        <v>95.90000000000001</v>
+        <v>104.5</v>
       </c>
       <c r="C21" t="n">
-        <v>407.9</v>
+        <v>441.9</v>
       </c>
     </row>
     <row r="22">
@@ -664,10 +664,10 @@
         <v>46266.34652777778</v>
       </c>
       <c r="B22" t="n">
-        <v>90.09999999999999</v>
+        <v>101.6</v>
       </c>
       <c r="C22" t="n">
-        <v>436.1</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23">
@@ -675,10 +675,10 @@
         <v>46266.34722222222</v>
       </c>
       <c r="B23" t="n">
-        <v>104.4</v>
+        <v>107.3</v>
       </c>
       <c r="C23" t="n">
-        <v>448.6</v>
+        <v>422.3</v>
       </c>
     </row>
     <row r="24">
@@ -686,10 +686,10 @@
         <v>46266.34791666667</v>
       </c>
       <c r="B24" t="n">
-        <v>105.2</v>
+        <v>99.7</v>
       </c>
       <c r="C24" t="n">
-        <v>425.4</v>
+        <v>416.6</v>
       </c>
     </row>
     <row r="25">
@@ -697,10 +697,10 @@
         <v>46266.34861111111</v>
       </c>
       <c r="B25" t="n">
-        <v>92.09999999999999</v>
+        <v>105.3</v>
       </c>
       <c r="C25" t="n">
-        <v>431.3</v>
+        <v>418.9</v>
       </c>
     </row>
     <row r="26">
@@ -708,10 +708,10 @@
         <v>46266.34930555556</v>
       </c>
       <c r="B26" t="n">
-        <v>106.8</v>
+        <v>108.7</v>
       </c>
       <c r="C26" t="n">
-        <v>425.4</v>
+        <v>443.5</v>
       </c>
     </row>
     <row r="27">
@@ -719,10 +719,10 @@
         <v>46266.35</v>
       </c>
       <c r="B27" t="n">
-        <v>94</v>
+        <v>109.6</v>
       </c>
       <c r="C27" t="n">
-        <v>418.7</v>
+        <v>411.9</v>
       </c>
     </row>
     <row r="28">
@@ -730,10 +730,10 @@
         <v>46266.35069444445</v>
       </c>
       <c r="B28" t="n">
-        <v>93.2</v>
+        <v>97.7</v>
       </c>
       <c r="C28" t="n">
-        <v>447.7</v>
+        <v>442.8</v>
       </c>
     </row>
     <row r="29">
@@ -741,10 +741,10 @@
         <v>46266.35138888889</v>
       </c>
       <c r="B29" t="n">
-        <v>108.4</v>
+        <v>98.2</v>
       </c>
       <c r="C29" t="n">
-        <v>445.9</v>
+        <v>415.9</v>
       </c>
     </row>
     <row r="30">
@@ -752,10 +752,10 @@
         <v>46266.35208333333</v>
       </c>
       <c r="B30" t="n">
-        <v>102</v>
+        <v>99.5</v>
       </c>
       <c r="C30" t="n">
-        <v>424.4</v>
+        <v>445.7</v>
       </c>
     </row>
     <row r="31">
@@ -763,10 +763,10 @@
         <v>46266.35277777778</v>
       </c>
       <c r="B31" t="n">
-        <v>92.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>418.1</v>
+        <v>449.4</v>
       </c>
     </row>
     <row r="32">
@@ -774,10 +774,10 @@
         <v>46266.35347222222</v>
       </c>
       <c r="B32" t="n">
-        <v>109.7</v>
+        <v>105.8</v>
       </c>
       <c r="C32" t="n">
-        <v>440.3</v>
+        <v>432.6</v>
       </c>
     </row>
     <row r="33">
@@ -785,10 +785,10 @@
         <v>46266.35416666666</v>
       </c>
       <c r="B33" t="n">
-        <v>94.8</v>
+        <v>93</v>
       </c>
       <c r="C33" t="n">
-        <v>412</v>
+        <v>448.2</v>
       </c>
     </row>
     <row r="34">
@@ -796,10 +796,10 @@
         <v>46266.35486111111</v>
       </c>
       <c r="B34" t="n">
-        <v>101.3</v>
+        <v>92.5</v>
       </c>
       <c r="C34" t="n">
-        <v>403.9</v>
+        <v>448.3</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         <v>46266.35555555556</v>
       </c>
       <c r="B35" t="n">
-        <v>104.6</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>440.8</v>
+        <v>405</v>
       </c>
     </row>
     <row r="36">
@@ -818,10 +818,10 @@
         <v>46266.35625</v>
       </c>
       <c r="B36" t="n">
-        <v>109.6</v>
+        <v>106.9</v>
       </c>
       <c r="C36" t="n">
-        <v>426.6</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37">
@@ -829,10 +829,10 @@
         <v>46266.35694444444</v>
       </c>
       <c r="B37" t="n">
-        <v>92.5</v>
+        <v>108.2</v>
       </c>
       <c r="C37" t="n">
-        <v>433</v>
+        <v>400.8</v>
       </c>
     </row>
     <row r="38">
@@ -840,10 +840,10 @@
         <v>46266.35763888889</v>
       </c>
       <c r="B38" t="n">
-        <v>108.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>408.3</v>
+        <v>443.5</v>
       </c>
     </row>
     <row r="39">
@@ -851,10 +851,10 @@
         <v>46266.35833333333</v>
       </c>
       <c r="B39" t="n">
-        <v>100.6</v>
+        <v>109.4</v>
       </c>
       <c r="C39" t="n">
-        <v>430.3</v>
+        <v>403.7</v>
       </c>
     </row>
     <row r="40">
@@ -862,10 +862,10 @@
         <v>46266.35902777778</v>
       </c>
       <c r="B40" t="n">
-        <v>109.3</v>
+        <v>105.6</v>
       </c>
       <c r="C40" t="n">
-        <v>446.4</v>
+        <v>413.3</v>
       </c>
     </row>
     <row r="41">
@@ -873,10 +873,10 @@
         <v>46266.35972222222</v>
       </c>
       <c r="B41" t="n">
-        <v>105.1</v>
+        <v>102.5</v>
       </c>
       <c r="C41" t="n">
-        <v>434.5</v>
+        <v>419.9</v>
       </c>
     </row>
     <row r="42">
@@ -884,10 +884,10 @@
         <v>46266.36041666667</v>
       </c>
       <c r="B42" t="n">
-        <v>104.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>419.9</v>
+        <v>416.4</v>
       </c>
     </row>
     <row r="43">
@@ -895,10 +895,10 @@
         <v>46266.36111111111</v>
       </c>
       <c r="B43" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="C43" t="n">
-        <v>418.7</v>
+        <v>426.7</v>
       </c>
     </row>
     <row r="44">
@@ -906,10 +906,10 @@
         <v>46266.36180555556</v>
       </c>
       <c r="B44" t="n">
-        <v>108</v>
+        <v>109.1</v>
       </c>
       <c r="C44" t="n">
-        <v>422.6</v>
+        <v>431.3</v>
       </c>
     </row>
     <row r="45">
@@ -917,10 +917,10 @@
         <v>46266.3625</v>
       </c>
       <c r="B45" t="n">
-        <v>95</v>
+        <v>107.7</v>
       </c>
       <c r="C45" t="n">
-        <v>403.2</v>
+        <v>424.4</v>
       </c>
     </row>
     <row r="46">
@@ -928,10 +928,10 @@
         <v>46266.36319444444</v>
       </c>
       <c r="B46" t="n">
-        <v>90.40000000000001</v>
+        <v>100.8</v>
       </c>
       <c r="C46" t="n">
-        <v>427.7</v>
+        <v>430.9</v>
       </c>
     </row>
     <row r="47">
@@ -939,10 +939,10 @@
         <v>46266.36388888889</v>
       </c>
       <c r="B47" t="n">
-        <v>101.8</v>
+        <v>94.7</v>
       </c>
       <c r="C47" t="n">
-        <v>400.4</v>
+        <v>434.2</v>
       </c>
     </row>
     <row r="48">
@@ -950,10 +950,10 @@
         <v>46266.36458333334</v>
       </c>
       <c r="B48" t="n">
-        <v>104.2</v>
+        <v>95.7</v>
       </c>
       <c r="C48" t="n">
-        <v>402.9</v>
+        <v>411.4</v>
       </c>
     </row>
     <row r="49">
@@ -961,10 +961,10 @@
         <v>46266.36527777778</v>
       </c>
       <c r="B49" t="n">
-        <v>91.3</v>
+        <v>91.8</v>
       </c>
       <c r="C49" t="n">
-        <v>401.6</v>
+        <v>448.9</v>
       </c>
     </row>
     <row r="50">
@@ -972,10 +972,10 @@
         <v>46266.36597222222</v>
       </c>
       <c r="B50" t="n">
-        <v>96.59999999999999</v>
+        <v>105.2</v>
       </c>
       <c r="C50" t="n">
-        <v>425.7</v>
+        <v>435.2</v>
       </c>
     </row>
     <row r="51">
@@ -983,10 +983,10 @@
         <v>46266.36666666667</v>
       </c>
       <c r="B51" t="n">
-        <v>95.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="C51" t="n">
-        <v>424.3</v>
+        <v>408.3</v>
       </c>
     </row>
     <row r="52">
@@ -994,10 +994,10 @@
         <v>46266.36736111111</v>
       </c>
       <c r="B52" t="n">
-        <v>100.8</v>
+        <v>96</v>
       </c>
       <c r="C52" t="n">
-        <v>436.2</v>
+        <v>401.4</v>
       </c>
     </row>
     <row r="53">
@@ -1008,7 +1008,7 @@
         <v>155</v>
       </c>
       <c r="C53" t="n">
-        <v>444.1</v>
+        <v>416.2</v>
       </c>
     </row>
     <row r="54">
@@ -1016,10 +1016,10 @@
         <v>46266.36875</v>
       </c>
       <c r="B54" t="n">
-        <v>101.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>412.1</v>
+        <v>417.9</v>
       </c>
     </row>
     <row r="55">
@@ -1027,10 +1027,10 @@
         <v>46266.36944444444</v>
       </c>
       <c r="B55" t="n">
-        <v>99.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>420.4</v>
+        <v>412.2</v>
       </c>
     </row>
     <row r="56">
@@ -1038,10 +1038,10 @@
         <v>46266.37013888889</v>
       </c>
       <c r="B56" t="n">
-        <v>91.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="C56" t="n">
-        <v>432.9</v>
+        <v>434.1</v>
       </c>
     </row>
     <row r="57">
@@ -1049,10 +1049,10 @@
         <v>46266.37083333333</v>
       </c>
       <c r="B57" t="n">
-        <v>97.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>420.6</v>
+        <v>408.8</v>
       </c>
     </row>
     <row r="58">
@@ -1060,10 +1060,10 @@
         <v>46266.37152777778</v>
       </c>
       <c r="B58" t="n">
-        <v>107.3</v>
+        <v>102.2</v>
       </c>
       <c r="C58" t="n">
-        <v>402.7</v>
+        <v>419.1</v>
       </c>
     </row>
     <row r="59">
@@ -1071,10 +1071,10 @@
         <v>46266.37222222222</v>
       </c>
       <c r="B59" t="n">
-        <v>103.1</v>
+        <v>103.7</v>
       </c>
       <c r="C59" t="n">
-        <v>432.3</v>
+        <v>424.9</v>
       </c>
     </row>
     <row r="60">
@@ -1082,10 +1082,10 @@
         <v>46266.37291666667</v>
       </c>
       <c r="B60" t="n">
-        <v>91.2</v>
+        <v>101.7</v>
       </c>
       <c r="C60" t="n">
-        <v>436.4</v>
+        <v>411.6</v>
       </c>
     </row>
     <row r="61">
@@ -1093,10 +1093,10 @@
         <v>46266.37361111111</v>
       </c>
       <c r="B61" t="n">
-        <v>106</v>
+        <v>102.8</v>
       </c>
       <c r="C61" t="n">
-        <v>405.5</v>
+        <v>423</v>
       </c>
     </row>
     <row r="62">
@@ -1104,10 +1104,10 @@
         <v>46266.37430555555</v>
       </c>
       <c r="B62" t="n">
-        <v>93.8</v>
+        <v>103.3</v>
       </c>
       <c r="C62" t="n">
-        <v>426.8</v>
+        <v>444.9</v>
       </c>
     </row>
     <row r="63">
@@ -1115,10 +1115,10 @@
         <v>46266.375</v>
       </c>
       <c r="B63" t="n">
-        <v>92.8</v>
+        <v>99.3</v>
       </c>
       <c r="C63" t="n">
-        <v>409.2</v>
+        <v>414.4</v>
       </c>
     </row>
     <row r="64">
@@ -1126,10 +1126,10 @@
         <v>46266.37569444445</v>
       </c>
       <c r="B64" t="n">
-        <v>99.3</v>
+        <v>100.9</v>
       </c>
       <c r="C64" t="n">
-        <v>443.7</v>
+        <v>403.7</v>
       </c>
     </row>
     <row r="65">
@@ -1137,10 +1137,10 @@
         <v>46266.37638888889</v>
       </c>
       <c r="B65" t="n">
-        <v>91.5</v>
+        <v>108.9</v>
       </c>
       <c r="C65" t="n">
-        <v>440.4</v>
+        <v>449.4</v>
       </c>
     </row>
     <row r="66">
@@ -1148,10 +1148,10 @@
         <v>46266.37708333333</v>
       </c>
       <c r="B66" t="n">
-        <v>107.1</v>
+        <v>96</v>
       </c>
       <c r="C66" t="n">
-        <v>404.9</v>
+        <v>448.1</v>
       </c>
     </row>
     <row r="67">
@@ -1159,10 +1159,10 @@
         <v>46266.37777777778</v>
       </c>
       <c r="B67" t="n">
-        <v>103</v>
+        <v>103.8</v>
       </c>
       <c r="C67" t="n">
-        <v>427</v>
+        <v>422.8</v>
       </c>
     </row>
     <row r="68">
@@ -1170,10 +1170,10 @@
         <v>46266.37847222222</v>
       </c>
       <c r="B68" t="n">
-        <v>90.3</v>
+        <v>96</v>
       </c>
       <c r="C68" t="n">
-        <v>404.7</v>
+        <v>450</v>
       </c>
     </row>
     <row r="69">
@@ -1181,10 +1181,10 @@
         <v>46266.37916666667</v>
       </c>
       <c r="B69" t="n">
-        <v>105.1</v>
+        <v>107.1</v>
       </c>
       <c r="C69" t="n">
-        <v>411.8</v>
+        <v>405.3</v>
       </c>
     </row>
     <row r="70">
@@ -1192,10 +1192,10 @@
         <v>46266.37986111111</v>
       </c>
       <c r="B70" t="n">
-        <v>98.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>424.1</v>
+        <v>417.9</v>
       </c>
     </row>
     <row r="71">
@@ -1203,10 +1203,10 @@
         <v>46266.38055555556</v>
       </c>
       <c r="B71" t="n">
-        <v>107.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C71" t="n">
-        <v>445.1</v>
+        <v>435</v>
       </c>
     </row>
     <row r="72">
@@ -1214,10 +1214,10 @@
         <v>46266.38125</v>
       </c>
       <c r="B72" t="n">
-        <v>93.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="C72" t="n">
-        <v>400.1</v>
+        <v>441.5</v>
       </c>
     </row>
     <row r="73">
@@ -1225,10 +1225,10 @@
         <v>46266.38194444445</v>
       </c>
       <c r="B73" t="n">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C73" t="n">
-        <v>446.3</v>
+        <v>400.4</v>
       </c>
     </row>
     <row r="74">
@@ -1236,10 +1236,10 @@
         <v>46266.38263888889</v>
       </c>
       <c r="B74" t="n">
-        <v>105.7</v>
+        <v>107.3</v>
       </c>
       <c r="C74" t="n">
-        <v>414.3</v>
+        <v>438.9</v>
       </c>
     </row>
     <row r="75">
@@ -1247,10 +1247,10 @@
         <v>46266.38333333333</v>
       </c>
       <c r="B75" t="n">
-        <v>103.9</v>
+        <v>109.5</v>
       </c>
       <c r="C75" t="n">
-        <v>436.5</v>
+        <v>445.5</v>
       </c>
     </row>
     <row r="76">
@@ -1258,10 +1258,10 @@
         <v>46266.38402777778</v>
       </c>
       <c r="B76" t="n">
-        <v>105.7</v>
+        <v>104.9</v>
       </c>
       <c r="C76" t="n">
-        <v>433.1</v>
+        <v>441.6</v>
       </c>
     </row>
     <row r="77">
@@ -1269,10 +1269,10 @@
         <v>46266.38472222222</v>
       </c>
       <c r="B77" t="n">
-        <v>99.7</v>
+        <v>108.1</v>
       </c>
       <c r="C77" t="n">
-        <v>409.5</v>
+        <v>438.8</v>
       </c>
     </row>
     <row r="78">
@@ -1280,10 +1280,10 @@
         <v>46266.38541666666</v>
       </c>
       <c r="B78" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="C78" t="n">
-        <v>402.9</v>
+        <v>440.1</v>
       </c>
     </row>
     <row r="79">
@@ -1291,10 +1291,10 @@
         <v>46266.38611111111</v>
       </c>
       <c r="B79" t="n">
-        <v>104.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>403</v>
+        <v>409.5</v>
       </c>
     </row>
     <row r="80">
@@ -1302,10 +1302,10 @@
         <v>46266.38680555556</v>
       </c>
       <c r="B80" t="n">
-        <v>96.3</v>
+        <v>95</v>
       </c>
       <c r="C80" t="n">
-        <v>402.5</v>
+        <v>437.8</v>
       </c>
     </row>
     <row r="81">
@@ -1313,10 +1313,10 @@
         <v>46266.3875</v>
       </c>
       <c r="B81" t="n">
-        <v>99.5</v>
+        <v>105.3</v>
       </c>
       <c r="C81" t="n">
-        <v>446</v>
+        <v>434</v>
       </c>
     </row>
     <row r="82">
@@ -1324,10 +1324,10 @@
         <v>46266.38819444444</v>
       </c>
       <c r="B82" t="n">
-        <v>100.6</v>
+        <v>92.7</v>
       </c>
       <c r="C82" t="n">
-        <v>402.8</v>
+        <v>404.9</v>
       </c>
     </row>
     <row r="83">
@@ -1335,10 +1335,10 @@
         <v>46266.38888888889</v>
       </c>
       <c r="B83" t="n">
-        <v>100.2</v>
+        <v>102.5</v>
       </c>
       <c r="C83" t="n">
-        <v>442.6</v>
+        <v>402</v>
       </c>
     </row>
     <row r="84">
@@ -1346,10 +1346,10 @@
         <v>46266.38958333333</v>
       </c>
       <c r="B84" t="n">
-        <v>91.40000000000001</v>
+        <v>105.8</v>
       </c>
       <c r="C84" t="n">
-        <v>403.4</v>
+        <v>401.7</v>
       </c>
     </row>
     <row r="85">
@@ -1357,10 +1357,10 @@
         <v>46266.39027777778</v>
       </c>
       <c r="B85" t="n">
-        <v>107.2</v>
+        <v>97.3</v>
       </c>
       <c r="C85" t="n">
-        <v>420.2</v>
+        <v>406.6</v>
       </c>
     </row>
     <row r="86">
@@ -1368,10 +1368,10 @@
         <v>46266.39097222222</v>
       </c>
       <c r="B86" t="n">
-        <v>108.8</v>
+        <v>108.2</v>
       </c>
       <c r="C86" t="n">
-        <v>428.5</v>
+        <v>416.3</v>
       </c>
     </row>
     <row r="87">
@@ -1379,10 +1379,10 @@
         <v>46266.39166666667</v>
       </c>
       <c r="B87" t="n">
-        <v>101.6</v>
+        <v>98.3</v>
       </c>
       <c r="C87" t="n">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="88">
@@ -1390,10 +1390,10 @@
         <v>46266.39236111111</v>
       </c>
       <c r="B88" t="n">
-        <v>91.59999999999999</v>
+        <v>105.7</v>
       </c>
       <c r="C88" t="n">
-        <v>432.9</v>
+        <v>443.8</v>
       </c>
     </row>
     <row r="89">
@@ -1401,10 +1401,10 @@
         <v>46266.39305555556</v>
       </c>
       <c r="B89" t="n">
-        <v>101.3</v>
+        <v>97.3</v>
       </c>
       <c r="C89" t="n">
-        <v>415.8</v>
+        <v>425.1</v>
       </c>
     </row>
     <row r="90">
@@ -1412,10 +1412,10 @@
         <v>46266.39375</v>
       </c>
       <c r="B90" t="n">
-        <v>95.2</v>
+        <v>95.5</v>
       </c>
       <c r="C90" t="n">
-        <v>433.5</v>
+        <v>408.2</v>
       </c>
     </row>
     <row r="91">
@@ -1423,10 +1423,10 @@
         <v>46266.39444444444</v>
       </c>
       <c r="B91" t="n">
-        <v>96.3</v>
+        <v>108.3</v>
       </c>
       <c r="C91" t="n">
-        <v>413.3</v>
+        <v>447.2</v>
       </c>
     </row>
     <row r="92">
@@ -1434,10 +1434,10 @@
         <v>46266.39513888889</v>
       </c>
       <c r="B92" t="n">
-        <v>92.59999999999999</v>
+        <v>109.3</v>
       </c>
       <c r="C92" t="n">
-        <v>432.3</v>
+        <v>414.8</v>
       </c>
     </row>
     <row r="93">
@@ -1445,10 +1445,10 @@
         <v>46266.39583333334</v>
       </c>
       <c r="B93" t="n">
-        <v>99.09999999999999</v>
+        <v>107.4</v>
       </c>
       <c r="C93" t="n">
-        <v>446.5</v>
+        <v>440.2</v>
       </c>
     </row>
     <row r="94">
@@ -1456,10 +1456,10 @@
         <v>46266.39652777778</v>
       </c>
       <c r="B94" t="n">
-        <v>108.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C94" t="n">
-        <v>400.5</v>
+        <v>403.8</v>
       </c>
     </row>
     <row r="95">
@@ -1467,10 +1467,10 @@
         <v>46266.39722222222</v>
       </c>
       <c r="B95" t="n">
-        <v>102.4</v>
+        <v>105.1</v>
       </c>
       <c r="C95" t="n">
-        <v>428.1</v>
+        <v>411.3</v>
       </c>
     </row>
     <row r="96">
@@ -1478,10 +1478,10 @@
         <v>46266.39791666667</v>
       </c>
       <c r="B96" t="n">
-        <v>92</v>
+        <v>103.5</v>
       </c>
       <c r="C96" t="n">
-        <v>426.9</v>
+        <v>433.7</v>
       </c>
     </row>
     <row r="97">
@@ -1489,10 +1489,10 @@
         <v>46266.39861111111</v>
       </c>
       <c r="B97" t="n">
-        <v>100.1</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>406.6</v>
+        <v>442.3</v>
       </c>
     </row>
     <row r="98">
@@ -1500,10 +1500,10 @@
         <v>46266.39930555555</v>
       </c>
       <c r="B98" t="n">
-        <v>97</v>
+        <v>101.1</v>
       </c>
       <c r="C98" t="n">
-        <v>403.4</v>
+        <v>404.5</v>
       </c>
     </row>
     <row r="99">
@@ -1511,10 +1511,10 @@
         <v>46266.4</v>
       </c>
       <c r="B99" t="n">
-        <v>94.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C99" t="n">
-        <v>414.2</v>
+        <v>413.2</v>
       </c>
     </row>
     <row r="100">
@@ -1522,10 +1522,10 @@
         <v>46266.40069444444</v>
       </c>
       <c r="B100" t="n">
-        <v>98.8</v>
+        <v>92.5</v>
       </c>
       <c r="C100" t="n">
-        <v>427.2</v>
+        <v>418.4</v>
       </c>
     </row>
     <row r="101">
@@ -1533,10 +1533,10 @@
         <v>46266.40138888889</v>
       </c>
       <c r="B101" t="n">
-        <v>96.09999999999999</v>
+        <v>105</v>
       </c>
       <c r="C101" t="n">
-        <v>449.2</v>
+        <v>413.1</v>
       </c>
     </row>
     <row r="102">
@@ -1544,10 +1544,10 @@
         <v>46266.40208333333</v>
       </c>
       <c r="B102" t="n">
-        <v>106.1</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C102" t="n">
-        <v>426.4</v>
+        <v>431.9</v>
       </c>
     </row>
     <row r="103">
@@ -1555,10 +1555,10 @@
         <v>46266.40277777778</v>
       </c>
       <c r="B103" t="n">
-        <v>103.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C103" t="n">
-        <v>427.7</v>
+        <v>433.7</v>
       </c>
     </row>
     <row r="104">
@@ -1566,10 +1566,10 @@
         <v>46266.40347222222</v>
       </c>
       <c r="B104" t="n">
-        <v>108.6</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C104" t="n">
-        <v>405.2</v>
+        <v>431</v>
       </c>
     </row>
     <row r="105">
@@ -1577,10 +1577,10 @@
         <v>46266.40416666667</v>
       </c>
       <c r="B105" t="n">
-        <v>107.6</v>
+        <v>108.9</v>
       </c>
       <c r="C105" t="n">
-        <v>413.2</v>
+        <v>416.4</v>
       </c>
     </row>
     <row r="106">
@@ -1588,10 +1588,10 @@
         <v>46266.40486111111</v>
       </c>
       <c r="B106" t="n">
-        <v>107.8</v>
+        <v>102.2</v>
       </c>
       <c r="C106" t="n">
-        <v>437.1</v>
+        <v>432.4</v>
       </c>
     </row>
     <row r="107">
@@ -1599,10 +1599,10 @@
         <v>46266.40555555555</v>
       </c>
       <c r="B107" t="n">
-        <v>93.09999999999999</v>
+        <v>102.7</v>
       </c>
       <c r="C107" t="n">
-        <v>414.1</v>
+        <v>423.2</v>
       </c>
     </row>
     <row r="108">
@@ -1610,10 +1610,10 @@
         <v>46266.40625</v>
       </c>
       <c r="B108" t="n">
-        <v>94.2</v>
+        <v>104</v>
       </c>
       <c r="C108" t="n">
-        <v>417.1</v>
+        <v>432.5</v>
       </c>
     </row>
     <row r="109">
@@ -1621,10 +1621,10 @@
         <v>46266.40694444445</v>
       </c>
       <c r="B109" t="n">
-        <v>103.7</v>
+        <v>92.3</v>
       </c>
       <c r="C109" t="n">
-        <v>442.6</v>
+        <v>402.3</v>
       </c>
     </row>
     <row r="110">
@@ -1632,10 +1632,10 @@
         <v>46266.40763888889</v>
       </c>
       <c r="B110" t="n">
-        <v>100.1</v>
+        <v>90.7</v>
       </c>
       <c r="C110" t="n">
-        <v>412.6</v>
+        <v>449.8</v>
       </c>
     </row>
     <row r="111">
@@ -1643,10 +1643,10 @@
         <v>46266.40833333333</v>
       </c>
       <c r="B111" t="n">
-        <v>108.2</v>
+        <v>92.3</v>
       </c>
       <c r="C111" t="n">
-        <v>402.5</v>
+        <v>411.7</v>
       </c>
     </row>
     <row r="112">
@@ -1654,10 +1654,10 @@
         <v>46266.40902777778</v>
       </c>
       <c r="B112" t="n">
-        <v>102.7</v>
+        <v>100.8</v>
       </c>
       <c r="C112" t="n">
-        <v>441.5</v>
+        <v>419.4</v>
       </c>
     </row>
     <row r="113">
@@ -1665,10 +1665,10 @@
         <v>46266.40972222222</v>
       </c>
       <c r="B113" t="n">
-        <v>90.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>416.7</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="114">
@@ -1676,10 +1676,10 @@
         <v>46266.41041666667</v>
       </c>
       <c r="B114" t="n">
-        <v>92.59999999999999</v>
+        <v>103.9</v>
       </c>
       <c r="C114" t="n">
-        <v>449</v>
+        <v>427</v>
       </c>
     </row>
     <row r="115">
@@ -1687,10 +1687,10 @@
         <v>46266.41111111111</v>
       </c>
       <c r="B115" t="n">
-        <v>93.2</v>
+        <v>101.7</v>
       </c>
       <c r="C115" t="n">
-        <v>422.1</v>
+        <v>436.3</v>
       </c>
     </row>
     <row r="116">
@@ -1698,10 +1698,10 @@
         <v>46266.41180555556</v>
       </c>
       <c r="B116" t="n">
-        <v>104.1</v>
+        <v>107.7</v>
       </c>
       <c r="C116" t="n">
-        <v>428</v>
+        <v>432.7</v>
       </c>
     </row>
     <row r="117">
@@ -1709,10 +1709,10 @@
         <v>46266.4125</v>
       </c>
       <c r="B117" t="n">
-        <v>92.2</v>
+        <v>106.7</v>
       </c>
       <c r="C117" t="n">
-        <v>447.3</v>
+        <v>430.8</v>
       </c>
     </row>
     <row r="118">
@@ -1720,10 +1720,10 @@
         <v>46266.41319444445</v>
       </c>
       <c r="B118" t="n">
-        <v>103.8</v>
+        <v>108.8</v>
       </c>
       <c r="C118" t="n">
-        <v>407.5</v>
+        <v>414</v>
       </c>
     </row>
     <row r="119">
@@ -1731,10 +1731,10 @@
         <v>46266.41388888889</v>
       </c>
       <c r="B119" t="n">
-        <v>90.7</v>
+        <v>103.8</v>
       </c>
       <c r="C119" t="n">
-        <v>418.5</v>
+        <v>410.9</v>
       </c>
     </row>
     <row r="120">
@@ -1742,10 +1742,10 @@
         <v>46266.41458333333</v>
       </c>
       <c r="B120" t="n">
-        <v>101.1</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C120" t="n">
-        <v>421.5</v>
+        <v>411.8</v>
       </c>
     </row>
     <row r="121">
@@ -1753,10 +1753,10 @@
         <v>46266.41527777778</v>
       </c>
       <c r="B121" t="n">
-        <v>90.8</v>
+        <v>97.3</v>
       </c>
       <c r="C121" t="n">
-        <v>418.2</v>
+        <v>449</v>
       </c>
     </row>
     <row r="122">
@@ -1764,10 +1764,10 @@
         <v>46266.41597222222</v>
       </c>
       <c r="B122" t="n">
-        <v>108.7</v>
+        <v>97.3</v>
       </c>
       <c r="C122" t="n">
-        <v>448.6</v>
+        <v>445.1</v>
       </c>
     </row>
     <row r="123">
@@ -1778,7 +1778,7 @@
         <v>160.2</v>
       </c>
       <c r="C123" t="n">
-        <v>402</v>
+        <v>432.2</v>
       </c>
     </row>
     <row r="124">
@@ -1786,10 +1786,10 @@
         <v>46266.41736111111</v>
       </c>
       <c r="B124" t="n">
-        <v>97.2</v>
+        <v>91.2</v>
       </c>
       <c r="C124" t="n">
-        <v>434.1</v>
+        <v>413.8</v>
       </c>
     </row>
     <row r="125">
@@ -1797,10 +1797,10 @@
         <v>46266.41805555556</v>
       </c>
       <c r="B125" t="n">
-        <v>103.3</v>
+        <v>109.4</v>
       </c>
       <c r="C125" t="n">
-        <v>417.7</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="126">
@@ -1808,10 +1808,10 @@
         <v>46266.41875</v>
       </c>
       <c r="B126" t="n">
-        <v>101.2</v>
+        <v>106.5</v>
       </c>
       <c r="C126" t="n">
-        <v>443.7</v>
+        <v>404.6</v>
       </c>
     </row>
     <row r="127">
@@ -1819,10 +1819,10 @@
         <v>46266.41944444444</v>
       </c>
       <c r="B127" t="n">
-        <v>109.5</v>
+        <v>94.2</v>
       </c>
       <c r="C127" t="n">
-        <v>437.5</v>
+        <v>432</v>
       </c>
     </row>
     <row r="128">
@@ -1830,10 +1830,10 @@
         <v>46266.42013888889</v>
       </c>
       <c r="B128" t="n">
-        <v>108.5</v>
+        <v>109.4</v>
       </c>
       <c r="C128" t="n">
-        <v>411.8</v>
+        <v>402.5</v>
       </c>
     </row>
     <row r="129">
@@ -1841,10 +1841,10 @@
         <v>46266.42083333333</v>
       </c>
       <c r="B129" t="n">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="C129" t="n">
-        <v>440</v>
+        <v>449.4</v>
       </c>
     </row>
     <row r="130">
@@ -1852,10 +1852,10 @@
         <v>46266.42152777778</v>
       </c>
       <c r="B130" t="n">
-        <v>93.5</v>
+        <v>105.7</v>
       </c>
       <c r="C130" t="n">
-        <v>420.6</v>
+        <v>410.3</v>
       </c>
     </row>
     <row r="131">
@@ -1863,10 +1863,10 @@
         <v>46266.42222222222</v>
       </c>
       <c r="B131" t="n">
-        <v>93.59999999999999</v>
+        <v>106.6</v>
       </c>
       <c r="C131" t="n">
-        <v>446.2</v>
+        <v>427.7</v>
       </c>
     </row>
     <row r="132">
@@ -1874,10 +1874,10 @@
         <v>46266.42291666667</v>
       </c>
       <c r="B132" t="n">
-        <v>105.6</v>
+        <v>101.7</v>
       </c>
       <c r="C132" t="n">
-        <v>420.6</v>
+        <v>440.7</v>
       </c>
     </row>
     <row r="133">
@@ -1885,10 +1885,10 @@
         <v>46266.42361111111</v>
       </c>
       <c r="B133" t="n">
-        <v>103.4</v>
+        <v>94.7</v>
       </c>
       <c r="C133" t="n">
-        <v>436.8</v>
+        <v>438.7</v>
       </c>
     </row>
     <row r="134">
@@ -1896,10 +1896,10 @@
         <v>46266.42430555556</v>
       </c>
       <c r="B134" t="n">
-        <v>95</v>
+        <v>105.8</v>
       </c>
       <c r="C134" t="n">
-        <v>408</v>
+        <v>429.8</v>
       </c>
     </row>
     <row r="135">
@@ -1907,10 +1907,10 @@
         <v>46266.425</v>
       </c>
       <c r="B135" t="n">
-        <v>104</v>
+        <v>95.5</v>
       </c>
       <c r="C135" t="n">
-        <v>419.1</v>
+        <v>449.2</v>
       </c>
     </row>
     <row r="136">
@@ -1918,10 +1918,10 @@
         <v>46266.42569444444</v>
       </c>
       <c r="B136" t="n">
-        <v>90.8</v>
+        <v>109.8</v>
       </c>
       <c r="C136" t="n">
-        <v>423.5</v>
+        <v>427</v>
       </c>
     </row>
     <row r="137">
@@ -1929,10 +1929,10 @@
         <v>46266.42638888889</v>
       </c>
       <c r="B137" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C137" t="n">
-        <v>445.9</v>
+        <v>405.5</v>
       </c>
     </row>
     <row r="138">
@@ -1940,10 +1940,10 @@
         <v>46266.42708333334</v>
       </c>
       <c r="B138" t="n">
-        <v>97</v>
+        <v>107.3</v>
       </c>
       <c r="C138" t="n">
-        <v>441</v>
+        <v>406.6</v>
       </c>
     </row>
     <row r="139">
@@ -1951,10 +1951,10 @@
         <v>46266.42777777778</v>
       </c>
       <c r="B139" t="n">
-        <v>107.4</v>
+        <v>97.2</v>
       </c>
       <c r="C139" t="n">
-        <v>411.1</v>
+        <v>439.4</v>
       </c>
     </row>
     <row r="140">
@@ -1962,10 +1962,10 @@
         <v>46266.42847222222</v>
       </c>
       <c r="B140" t="n">
-        <v>103.2</v>
+        <v>101.8</v>
       </c>
       <c r="C140" t="n">
-        <v>419.9</v>
+        <v>400.8</v>
       </c>
     </row>
     <row r="141">
@@ -1973,10 +1973,10 @@
         <v>46266.42916666667</v>
       </c>
       <c r="B141" t="n">
-        <v>95.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="C141" t="n">
-        <v>403.5</v>
+        <v>406.3</v>
       </c>
     </row>
     <row r="142">
@@ -1984,10 +1984,10 @@
         <v>46266.42986111111</v>
       </c>
       <c r="B142" t="n">
-        <v>105.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="C142" t="n">
-        <v>417.6</v>
+        <v>405.7</v>
       </c>
     </row>
     <row r="143">
@@ -1995,10 +1995,10 @@
         <v>46266.43055555555</v>
       </c>
       <c r="B143" t="n">
-        <v>100.2</v>
+        <v>91.3</v>
       </c>
       <c r="C143" t="n">
-        <v>434</v>
+        <v>422.4</v>
       </c>
     </row>
     <row r="144">
@@ -2006,10 +2006,10 @@
         <v>46266.43125</v>
       </c>
       <c r="B144" t="n">
-        <v>106.9</v>
+        <v>97.2</v>
       </c>
       <c r="C144" t="n">
-        <v>416.6</v>
+        <v>429.7</v>
       </c>
     </row>
     <row r="145">
@@ -2017,10 +2017,10 @@
         <v>46266.43194444444</v>
       </c>
       <c r="B145" t="n">
-        <v>90.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="C145" t="n">
-        <v>443.9</v>
+        <v>411.1</v>
       </c>
     </row>
     <row r="146">
@@ -2028,10 +2028,10 @@
         <v>46266.43263888889</v>
       </c>
       <c r="B146" t="n">
-        <v>95.2</v>
+        <v>102.3</v>
       </c>
       <c r="C146" t="n">
-        <v>429</v>
+        <v>436.4</v>
       </c>
     </row>
     <row r="147">
@@ -2039,10 +2039,10 @@
         <v>46266.43333333333</v>
       </c>
       <c r="B147" t="n">
-        <v>109.7</v>
+        <v>108.2</v>
       </c>
       <c r="C147" t="n">
-        <v>401.9</v>
+        <v>432.9</v>
       </c>
     </row>
     <row r="148">
@@ -2050,10 +2050,10 @@
         <v>46266.43402777778</v>
       </c>
       <c r="B148" t="n">
-        <v>101.9</v>
+        <v>96</v>
       </c>
       <c r="C148" t="n">
-        <v>417.3</v>
+        <v>432.2</v>
       </c>
     </row>
     <row r="149">
@@ -2061,10 +2061,10 @@
         <v>46266.43472222222</v>
       </c>
       <c r="B149" t="n">
-        <v>105.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="C149" t="n">
-        <v>421.8</v>
+        <v>449.9</v>
       </c>
     </row>
     <row r="150">
@@ -2072,10 +2072,10 @@
         <v>46266.43541666667</v>
       </c>
       <c r="B150" t="n">
-        <v>109.7</v>
+        <v>106.9</v>
       </c>
       <c r="C150" t="n">
-        <v>405.8</v>
+        <v>421.3</v>
       </c>
     </row>
     <row r="151">
@@ -2083,10 +2083,10 @@
         <v>46266.43611111111</v>
       </c>
       <c r="B151" t="n">
-        <v>108</v>
+        <v>92.2</v>
       </c>
       <c r="C151" t="n">
-        <v>409.5</v>
+        <v>435.6</v>
       </c>
     </row>
     <row r="152">
@@ -2094,10 +2094,10 @@
         <v>46266.43680555555</v>
       </c>
       <c r="B152" t="n">
-        <v>90.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C152" t="n">
-        <v>421.8</v>
+        <v>445</v>
       </c>
     </row>
     <row r="153">
@@ -2105,10 +2105,10 @@
         <v>46266.4375</v>
       </c>
       <c r="B153" t="n">
-        <v>100.4</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="C153" t="n">
-        <v>440.3</v>
+        <v>407.4</v>
       </c>
     </row>
     <row r="154">
@@ -2116,10 +2116,10 @@
         <v>46266.43819444445</v>
       </c>
       <c r="B154" t="n">
-        <v>103.7</v>
+        <v>92.5</v>
       </c>
       <c r="C154" t="n">
-        <v>447</v>
+        <v>431.2</v>
       </c>
     </row>
     <row r="155">
@@ -2127,10 +2127,10 @@
         <v>46266.43888888889</v>
       </c>
       <c r="B155" t="n">
-        <v>104.7</v>
+        <v>101.7</v>
       </c>
       <c r="C155" t="n">
-        <v>409.9</v>
+        <v>435.6</v>
       </c>
     </row>
     <row r="156">
@@ -2138,10 +2138,10 @@
         <v>46266.43958333333</v>
       </c>
       <c r="B156" t="n">
-        <v>98.59999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C156" t="n">
-        <v>447.4</v>
+        <v>429.9</v>
       </c>
     </row>
     <row r="157">
@@ -2149,10 +2149,10 @@
         <v>46266.44027777778</v>
       </c>
       <c r="B157" t="n">
-        <v>108.4</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C157" t="n">
-        <v>431.2</v>
+        <v>425.3</v>
       </c>
     </row>
     <row r="158">
@@ -2160,10 +2160,10 @@
         <v>46266.44097222222</v>
       </c>
       <c r="B158" t="n">
-        <v>103.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C158" t="n">
-        <v>406.2</v>
+        <v>439.7</v>
       </c>
     </row>
     <row r="159">
@@ -2171,10 +2171,10 @@
         <v>46266.44166666667</v>
       </c>
       <c r="B159" t="n">
-        <v>108</v>
+        <v>92.3</v>
       </c>
       <c r="C159" t="n">
-        <v>425.4</v>
+        <v>432.7</v>
       </c>
     </row>
     <row r="160">
@@ -2182,10 +2182,10 @@
         <v>46266.44236111111</v>
       </c>
       <c r="B160" t="n">
-        <v>103.3</v>
+        <v>107.6</v>
       </c>
       <c r="C160" t="n">
-        <v>416.3</v>
+        <v>427.6</v>
       </c>
     </row>
     <row r="161">
@@ -2193,10 +2193,10 @@
         <v>46266.44305555556</v>
       </c>
       <c r="B161" t="n">
-        <v>103.9</v>
+        <v>107.3</v>
       </c>
       <c r="C161" t="n">
-        <v>427.7</v>
+        <v>421.5</v>
       </c>
     </row>
     <row r="162">
@@ -2204,10 +2204,10 @@
         <v>46266.44375</v>
       </c>
       <c r="B162" t="n">
-        <v>93.8</v>
+        <v>107.8</v>
       </c>
       <c r="C162" t="n">
-        <v>433.2</v>
+        <v>420.7</v>
       </c>
     </row>
     <row r="163">
@@ -2215,10 +2215,10 @@
         <v>46266.44444444445</v>
       </c>
       <c r="B163" t="n">
-        <v>97.59999999999999</v>
+        <v>106.5</v>
       </c>
       <c r="C163" t="n">
-        <v>437.4</v>
+        <v>419.9</v>
       </c>
     </row>
     <row r="164">
@@ -2226,10 +2226,10 @@
         <v>46266.44513888889</v>
       </c>
       <c r="B164" t="n">
-        <v>93.5</v>
+        <v>104.6</v>
       </c>
       <c r="C164" t="n">
-        <v>428.5</v>
+        <v>415.6</v>
       </c>
     </row>
     <row r="165">
@@ -2237,10 +2237,10 @@
         <v>46266.44583333333</v>
       </c>
       <c r="B165" t="n">
-        <v>98.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="C165" t="n">
-        <v>441.7</v>
+        <v>412.7</v>
       </c>
     </row>
     <row r="166">
@@ -2248,10 +2248,10 @@
         <v>46266.44652777778</v>
       </c>
       <c r="B166" t="n">
-        <v>96.09999999999999</v>
+        <v>109.1</v>
       </c>
       <c r="C166" t="n">
-        <v>410.5</v>
+        <v>434.3</v>
       </c>
     </row>
     <row r="167">
@@ -2259,10 +2259,10 @@
         <v>46266.44722222222</v>
       </c>
       <c r="B167" t="n">
-        <v>105.7</v>
+        <v>99.5</v>
       </c>
       <c r="C167" t="n">
-        <v>430.3</v>
+        <v>404.6</v>
       </c>
     </row>
     <row r="168">
@@ -2270,10 +2270,10 @@
         <v>46266.44791666666</v>
       </c>
       <c r="B168" t="n">
-        <v>96.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="C168" t="n">
-        <v>422.1</v>
+        <v>421.6</v>
       </c>
     </row>
     <row r="169">
@@ -2281,10 +2281,10 @@
         <v>46266.44861111111</v>
       </c>
       <c r="B169" t="n">
-        <v>103.5</v>
+        <v>104.9</v>
       </c>
       <c r="C169" t="n">
-        <v>425.6</v>
+        <v>418.6</v>
       </c>
     </row>
     <row r="170">
@@ -2292,10 +2292,10 @@
         <v>46266.44930555556</v>
       </c>
       <c r="B170" t="n">
-        <v>105.9</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C170" t="n">
-        <v>448</v>
+        <v>403</v>
       </c>
     </row>
     <row r="171">
@@ -2303,10 +2303,10 @@
         <v>46266.45</v>
       </c>
       <c r="B171" t="n">
-        <v>104.7</v>
+        <v>109.1</v>
       </c>
       <c r="C171" t="n">
-        <v>432.9</v>
+        <v>428.1</v>
       </c>
     </row>
     <row r="172">
@@ -2314,10 +2314,10 @@
         <v>46266.45069444444</v>
       </c>
       <c r="B172" t="n">
-        <v>95.7</v>
+        <v>103.4</v>
       </c>
       <c r="C172" t="n">
-        <v>433.2</v>
+        <v>420.5</v>
       </c>
     </row>
     <row r="173">
@@ -2325,10 +2325,10 @@
         <v>46266.45138888889</v>
       </c>
       <c r="B173" t="n">
-        <v>102.4</v>
+        <v>107.5</v>
       </c>
       <c r="C173" t="n">
-        <v>404.7</v>
+        <v>447.1</v>
       </c>
     </row>
     <row r="174">
@@ -2336,10 +2336,10 @@
         <v>46266.45208333333</v>
       </c>
       <c r="B174" t="n">
-        <v>109</v>
+        <v>98.5</v>
       </c>
       <c r="C174" t="n">
-        <v>411.7</v>
+        <v>445.8</v>
       </c>
     </row>
     <row r="175">
@@ -2347,10 +2347,10 @@
         <v>46266.45277777778</v>
       </c>
       <c r="B175" t="n">
-        <v>96.2</v>
+        <v>91</v>
       </c>
       <c r="C175" t="n">
-        <v>440.3</v>
+        <v>414.4</v>
       </c>
     </row>
     <row r="176">
@@ -2358,10 +2358,10 @@
         <v>46266.45347222222</v>
       </c>
       <c r="B176" t="n">
-        <v>92.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="C176" t="n">
-        <v>402.3</v>
+        <v>405.2</v>
       </c>
     </row>
     <row r="177">
@@ -2369,10 +2369,10 @@
         <v>46266.45416666667</v>
       </c>
       <c r="B177" t="n">
-        <v>109.7</v>
+        <v>100.1</v>
       </c>
       <c r="C177" t="n">
-        <v>430.6</v>
+        <v>407.7</v>
       </c>
     </row>
     <row r="178">
@@ -2380,10 +2380,10 @@
         <v>46266.45486111111</v>
       </c>
       <c r="B178" t="n">
-        <v>105.4</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C178" t="n">
-        <v>422.8</v>
+        <v>442.4</v>
       </c>
     </row>
     <row r="179">
@@ -2391,10 +2391,10 @@
         <v>46266.45555555556</v>
       </c>
       <c r="B179" t="n">
-        <v>107.7</v>
+        <v>97</v>
       </c>
       <c r="C179" t="n">
-        <v>428.8</v>
+        <v>427.8</v>
       </c>
     </row>
     <row r="180">
@@ -2402,10 +2402,10 @@
         <v>46266.45625</v>
       </c>
       <c r="B180" t="n">
-        <v>104.4</v>
+        <v>92.3</v>
       </c>
       <c r="C180" t="n">
-        <v>419.2</v>
+        <v>413.9</v>
       </c>
     </row>
     <row r="181">
@@ -2413,10 +2413,10 @@
         <v>46266.45694444444</v>
       </c>
       <c r="B181" t="n">
-        <v>98</v>
+        <v>94.5</v>
       </c>
       <c r="C181" t="n">
-        <v>407.4</v>
+        <v>421.5</v>
       </c>
     </row>
     <row r="182">
@@ -2424,10 +2424,10 @@
         <v>46266.45763888889</v>
       </c>
       <c r="B182" t="n">
-        <v>103.8</v>
+        <v>101.2</v>
       </c>
       <c r="C182" t="n">
-        <v>444.6</v>
+        <v>438.4</v>
       </c>
     </row>
     <row r="183">
@@ -2435,10 +2435,10 @@
         <v>46266.45833333334</v>
       </c>
       <c r="B183" t="n">
-        <v>107.2</v>
+        <v>102.4</v>
       </c>
       <c r="C183" t="n">
-        <v>444.3</v>
+        <v>433.7</v>
       </c>
     </row>
     <row r="184">
@@ -2446,10 +2446,10 @@
         <v>46266.45902777778</v>
       </c>
       <c r="B184" t="n">
-        <v>105.6</v>
+        <v>101.1</v>
       </c>
       <c r="C184" t="n">
-        <v>410.9</v>
+        <v>430.4</v>
       </c>
     </row>
     <row r="185">
@@ -2457,10 +2457,10 @@
         <v>46266.45972222222</v>
       </c>
       <c r="B185" t="n">
-        <v>106.1</v>
+        <v>103.2</v>
       </c>
       <c r="C185" t="n">
-        <v>434.8</v>
+        <v>434.7</v>
       </c>
     </row>
     <row r="186">
@@ -2468,10 +2468,10 @@
         <v>46266.46041666667</v>
       </c>
       <c r="B186" t="n">
-        <v>99.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="C186" t="n">
-        <v>427.9</v>
+        <v>413.7</v>
       </c>
     </row>
     <row r="187">
@@ -2479,10 +2479,10 @@
         <v>46266.46111111111</v>
       </c>
       <c r="B187" t="n">
-        <v>108.3</v>
+        <v>105.2</v>
       </c>
       <c r="C187" t="n">
-        <v>406.1</v>
+        <v>446.1</v>
       </c>
     </row>
     <row r="188">
@@ -2490,10 +2490,10 @@
         <v>46266.46180555555</v>
       </c>
       <c r="B188" t="n">
-        <v>92.7</v>
+        <v>97</v>
       </c>
       <c r="C188" t="n">
-        <v>423.2</v>
+        <v>409.1</v>
       </c>
     </row>
     <row r="189">
@@ -2501,10 +2501,10 @@
         <v>46266.4625</v>
       </c>
       <c r="B189" t="n">
-        <v>100.6</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="C189" t="n">
-        <v>427.9</v>
+        <v>432.9</v>
       </c>
     </row>
     <row r="190">
@@ -2512,10 +2512,10 @@
         <v>46266.46319444444</v>
       </c>
       <c r="B190" t="n">
-        <v>96.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="C190" t="n">
-        <v>437.8</v>
+        <v>437</v>
       </c>
     </row>
     <row r="191">
@@ -2523,10 +2523,10 @@
         <v>46266.46388888889</v>
       </c>
       <c r="B191" t="n">
-        <v>98.90000000000001</v>
+        <v>109.4</v>
       </c>
       <c r="C191" t="n">
-        <v>440.8</v>
+        <v>404.6</v>
       </c>
     </row>
     <row r="192">
@@ -2534,10 +2534,10 @@
         <v>46266.46458333333</v>
       </c>
       <c r="B192" t="n">
-        <v>107.8</v>
+        <v>100.6</v>
       </c>
       <c r="C192" t="n">
-        <v>421.3</v>
+        <v>418.8</v>
       </c>
     </row>
     <row r="193">
@@ -2545,10 +2545,10 @@
         <v>46266.46527777778</v>
       </c>
       <c r="B193" t="n">
-        <v>108.1</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="C193" t="n">
-        <v>422.3</v>
+        <v>407.9</v>
       </c>
     </row>
     <row r="194">
@@ -2556,10 +2556,10 @@
         <v>46266.46597222222</v>
       </c>
       <c r="B194" t="n">
-        <v>93.2</v>
+        <v>96.2</v>
       </c>
       <c r="C194" t="n">
-        <v>443.1</v>
+        <v>416.2</v>
       </c>
     </row>
     <row r="195">
@@ -2567,10 +2567,10 @@
         <v>46266.46666666667</v>
       </c>
       <c r="B195" t="n">
-        <v>99</v>
+        <v>108.8</v>
       </c>
       <c r="C195" t="n">
-        <v>437.6</v>
+        <v>429.8</v>
       </c>
     </row>
     <row r="196">
@@ -2578,10 +2578,10 @@
         <v>46266.46736111111</v>
       </c>
       <c r="B196" t="n">
-        <v>106.8</v>
+        <v>107.7</v>
       </c>
       <c r="C196" t="n">
-        <v>413.9</v>
+        <v>407.8</v>
       </c>
     </row>
     <row r="197">
@@ -2589,10 +2589,10 @@
         <v>46266.46805555555</v>
       </c>
       <c r="B197" t="n">
-        <v>105.6</v>
+        <v>105.1</v>
       </c>
       <c r="C197" t="n">
-        <v>424.2</v>
+        <v>402.5</v>
       </c>
     </row>
     <row r="198">
@@ -2600,10 +2600,10 @@
         <v>46266.46875</v>
       </c>
       <c r="B198" t="n">
-        <v>94.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="C198" t="n">
-        <v>422</v>
+        <v>422.2</v>
       </c>
     </row>
     <row r="199">
@@ -2611,10 +2611,10 @@
         <v>46266.46944444445</v>
       </c>
       <c r="B199" t="n">
-        <v>104.3</v>
+        <v>98.5</v>
       </c>
       <c r="C199" t="n">
-        <v>411.7</v>
+        <v>430.4</v>
       </c>
     </row>
     <row r="200">
@@ -2622,10 +2622,10 @@
         <v>46266.47013888889</v>
       </c>
       <c r="B200" t="n">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="C200" t="n">
-        <v>444.7</v>
+        <v>410.8</v>
       </c>
     </row>
     <row r="201">
@@ -2633,10 +2633,10 @@
         <v>46266.47083333333</v>
       </c>
       <c r="B201" t="n">
-        <v>91.59999999999999</v>
+        <v>100.2</v>
       </c>
       <c r="C201" t="n">
-        <v>407.5</v>
+        <v>417.3</v>
       </c>
     </row>
     <row r="202">
@@ -2644,10 +2644,10 @@
         <v>46266.47152777778</v>
       </c>
       <c r="B202" t="n">
-        <v>97.7</v>
+        <v>92.2</v>
       </c>
       <c r="C202" t="n">
-        <v>407.6</v>
+        <v>433.9</v>
       </c>
     </row>
     <row r="203">
@@ -2655,10 +2655,10 @@
         <v>46266.47222222222</v>
       </c>
       <c r="B203" t="n">
-        <v>94.3</v>
+        <v>101.9</v>
       </c>
       <c r="C203" t="n">
-        <v>420.7</v>
+        <v>426.3</v>
       </c>
     </row>
     <row r="204">
@@ -2666,10 +2666,10 @@
         <v>46266.47291666667</v>
       </c>
       <c r="B204" t="n">
-        <v>96.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="C204" t="n">
-        <v>423.3</v>
+        <v>411</v>
       </c>
     </row>
     <row r="205">
@@ -2677,10 +2677,10 @@
         <v>46266.47361111111</v>
       </c>
       <c r="B205" t="n">
-        <v>91.2</v>
+        <v>109.7</v>
       </c>
       <c r="C205" t="n">
-        <v>441.6</v>
+        <v>402.7</v>
       </c>
     </row>
     <row r="206">
@@ -2688,10 +2688,10 @@
         <v>46266.47430555556</v>
       </c>
       <c r="B206" t="n">
-        <v>97.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C206" t="n">
-        <v>438.5</v>
+        <v>447.3</v>
       </c>
     </row>
     <row r="207">
@@ -2699,10 +2699,10 @@
         <v>46266.475</v>
       </c>
       <c r="B207" t="n">
-        <v>108.9</v>
+        <v>105.3</v>
       </c>
       <c r="C207" t="n">
-        <v>401</v>
+        <v>438.2</v>
       </c>
     </row>
     <row r="208">
@@ -2710,10 +2710,10 @@
         <v>46266.47569444445</v>
       </c>
       <c r="B208" t="n">
-        <v>107.6</v>
+        <v>95.8</v>
       </c>
       <c r="C208" t="n">
-        <v>428.8</v>
+        <v>406</v>
       </c>
     </row>
     <row r="209">
@@ -2721,10 +2721,10 @@
         <v>46266.47638888889</v>
       </c>
       <c r="B209" t="n">
-        <v>99.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C209" t="n">
-        <v>447.1</v>
+        <v>421.5</v>
       </c>
     </row>
     <row r="210">
@@ -2732,10 +2732,10 @@
         <v>46266.47708333333</v>
       </c>
       <c r="B210" t="n">
-        <v>96</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C210" t="n">
-        <v>419.5</v>
+        <v>426.6</v>
       </c>
     </row>
     <row r="211">
@@ -2743,10 +2743,10 @@
         <v>46266.47777777778</v>
       </c>
       <c r="B211" t="n">
-        <v>107.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="C211" t="n">
-        <v>441.8</v>
+        <v>427.9</v>
       </c>
     </row>
     <row r="212">
@@ -2754,10 +2754,10 @@
         <v>46266.47847222222</v>
       </c>
       <c r="B212" t="n">
-        <v>100.8</v>
+        <v>103.4</v>
       </c>
       <c r="C212" t="n">
-        <v>436.7</v>
+        <v>417.7</v>
       </c>
     </row>
     <row r="213">
@@ -2765,10 +2765,10 @@
         <v>46266.47916666666</v>
       </c>
       <c r="B213" t="n">
-        <v>106</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C213" t="n">
-        <v>444.9</v>
+        <v>437.1</v>
       </c>
     </row>
     <row r="214">
@@ -2776,10 +2776,10 @@
         <v>46266.47986111111</v>
       </c>
       <c r="B214" t="n">
-        <v>99.8</v>
+        <v>98.7</v>
       </c>
       <c r="C214" t="n">
-        <v>413.6</v>
+        <v>423</v>
       </c>
     </row>
     <row r="215">
@@ -2787,10 +2787,10 @@
         <v>46266.48055555556</v>
       </c>
       <c r="B215" t="n">
-        <v>99.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="C215" t="n">
-        <v>419.4</v>
+        <v>415.7</v>
       </c>
     </row>
     <row r="216">
@@ -2798,10 +2798,10 @@
         <v>46266.48125</v>
       </c>
       <c r="B216" t="n">
-        <v>103.4</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C216" t="n">
-        <v>439.9</v>
+        <v>420.2</v>
       </c>
     </row>
     <row r="217">
@@ -2809,10 +2809,10 @@
         <v>46266.48194444444</v>
       </c>
       <c r="B217" t="n">
-        <v>104.5</v>
+        <v>102.8</v>
       </c>
       <c r="C217" t="n">
-        <v>442</v>
+        <v>414.5</v>
       </c>
     </row>
     <row r="218">
@@ -2820,10 +2820,10 @@
         <v>46266.48263888889</v>
       </c>
       <c r="B218" t="n">
-        <v>108.4</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C218" t="n">
-        <v>449</v>
+        <v>448.3</v>
       </c>
     </row>
     <row r="219">
@@ -2831,10 +2831,10 @@
         <v>46266.48333333333</v>
       </c>
       <c r="B219" t="n">
-        <v>100.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="C219" t="n">
-        <v>445.3</v>
+        <v>447.4</v>
       </c>
     </row>
     <row r="220">
@@ -2842,10 +2842,10 @@
         <v>46266.48402777778</v>
       </c>
       <c r="B220" t="n">
-        <v>101.8</v>
+        <v>99.2</v>
       </c>
       <c r="C220" t="n">
-        <v>433.1</v>
+        <v>434.5</v>
       </c>
     </row>
     <row r="221">
@@ -2853,10 +2853,10 @@
         <v>46266.48472222222</v>
       </c>
       <c r="B221" t="n">
-        <v>91.7</v>
+        <v>97.2</v>
       </c>
       <c r="C221" t="n">
-        <v>421.4</v>
+        <v>421.8</v>
       </c>
     </row>
     <row r="222">
@@ -2864,10 +2864,10 @@
         <v>46266.48541666667</v>
       </c>
       <c r="B222" t="n">
-        <v>107.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C222" t="n">
-        <v>409.1</v>
+        <v>421.8</v>
       </c>
     </row>
     <row r="223">
@@ -2875,10 +2875,10 @@
         <v>46266.48611111111</v>
       </c>
       <c r="B223" t="n">
-        <v>95.2</v>
+        <v>98</v>
       </c>
       <c r="C223" t="n">
-        <v>416.4</v>
+        <v>403.9</v>
       </c>
     </row>
     <row r="224">
@@ -2886,10 +2886,10 @@
         <v>46266.48680555556</v>
       </c>
       <c r="B224" t="n">
-        <v>99.09999999999999</v>
+        <v>107.4</v>
       </c>
       <c r="C224" t="n">
-        <v>416.9</v>
+        <v>437.3</v>
       </c>
     </row>
     <row r="225">
@@ -2897,10 +2897,10 @@
         <v>46266.4875</v>
       </c>
       <c r="B225" t="n">
-        <v>107.6</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C225" t="n">
-        <v>413.9</v>
+        <v>439</v>
       </c>
     </row>
     <row r="226">
@@ -2908,10 +2908,10 @@
         <v>46266.48819444444</v>
       </c>
       <c r="B226" t="n">
-        <v>109</v>
+        <v>91.5</v>
       </c>
       <c r="C226" t="n">
-        <v>421.1</v>
+        <v>431.7</v>
       </c>
     </row>
     <row r="227">
@@ -2919,10 +2919,10 @@
         <v>46266.48888888889</v>
       </c>
       <c r="B227" t="n">
-        <v>106.7</v>
+        <v>100.6</v>
       </c>
       <c r="C227" t="n">
-        <v>423.5</v>
+        <v>409.7</v>
       </c>
     </row>
     <row r="228">
@@ -2930,10 +2930,10 @@
         <v>46266.48958333334</v>
       </c>
       <c r="B228" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="C228" t="n">
-        <v>402.6</v>
+        <v>417.6</v>
       </c>
     </row>
     <row r="229">
@@ -2941,10 +2941,10 @@
         <v>46266.49027777778</v>
       </c>
       <c r="B229" t="n">
-        <v>109</v>
+        <v>109.2</v>
       </c>
       <c r="C229" t="n">
-        <v>411.2</v>
+        <v>432.3</v>
       </c>
     </row>
     <row r="230">
@@ -2952,10 +2952,10 @@
         <v>46266.49097222222</v>
       </c>
       <c r="B230" t="n">
-        <v>91.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="C230" t="n">
-        <v>447.9</v>
+        <v>405.1</v>
       </c>
     </row>
     <row r="231">
@@ -2963,10 +2963,10 @@
         <v>46266.49166666667</v>
       </c>
       <c r="B231" t="n">
-        <v>90.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="C231" t="n">
-        <v>401.6</v>
+        <v>408.7</v>
       </c>
     </row>
     <row r="232">
@@ -2974,10 +2974,10 @@
         <v>46266.49236111111</v>
       </c>
       <c r="B232" t="n">
-        <v>94.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="C232" t="n">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="233">
@@ -2985,10 +2985,10 @@
         <v>46266.49305555555</v>
       </c>
       <c r="B233" t="n">
-        <v>102.4</v>
+        <v>91.5</v>
       </c>
       <c r="C233" t="n">
-        <v>411.9</v>
+        <v>447.6</v>
       </c>
     </row>
     <row r="234">
@@ -2996,10 +2996,10 @@
         <v>46266.49375</v>
       </c>
       <c r="B234" t="n">
-        <v>99.5</v>
+        <v>102.6</v>
       </c>
       <c r="C234" t="n">
-        <v>405.7</v>
+        <v>423.2</v>
       </c>
     </row>
     <row r="235">
@@ -3007,10 +3007,10 @@
         <v>46266.49444444444</v>
       </c>
       <c r="B235" t="n">
-        <v>109</v>
+        <v>101.3</v>
       </c>
       <c r="C235" t="n">
-        <v>423.3</v>
+        <v>429</v>
       </c>
     </row>
     <row r="236">
@@ -3018,10 +3018,10 @@
         <v>46266.49513888889</v>
       </c>
       <c r="B236" t="n">
-        <v>95.09999999999999</v>
+        <v>103.6</v>
       </c>
       <c r="C236" t="n">
-        <v>418.4</v>
+        <v>444.1</v>
       </c>
     </row>
     <row r="237">
@@ -3029,10 +3029,10 @@
         <v>46266.49583333333</v>
       </c>
       <c r="B237" t="n">
-        <v>102.1</v>
+        <v>102.9</v>
       </c>
       <c r="C237" t="n">
-        <v>448.2</v>
+        <v>449.3</v>
       </c>
     </row>
     <row r="238">
@@ -3040,10 +3040,10 @@
         <v>46266.49652777778</v>
       </c>
       <c r="B238" t="n">
-        <v>104.4</v>
+        <v>96.5</v>
       </c>
       <c r="C238" t="n">
-        <v>438.9</v>
+        <v>448.5</v>
       </c>
     </row>
     <row r="239">
@@ -3051,10 +3051,10 @@
         <v>46266.49722222222</v>
       </c>
       <c r="B239" t="n">
-        <v>93.3</v>
+        <v>96.3</v>
       </c>
       <c r="C239" t="n">
-        <v>415.6</v>
+        <v>422</v>
       </c>
     </row>
     <row r="240">
@@ -3062,10 +3062,10 @@
         <v>46266.49791666667</v>
       </c>
       <c r="B240" t="n">
-        <v>101.6</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C240" t="n">
-        <v>446.4</v>
+        <v>431.6</v>
       </c>
     </row>
     <row r="241">
@@ -3073,10 +3073,10 @@
         <v>46266.49861111111</v>
       </c>
       <c r="B241" t="n">
-        <v>101.5</v>
+        <v>105.9</v>
       </c>
       <c r="C241" t="n">
-        <v>445.4</v>
+        <v>429.6</v>
       </c>
     </row>
     <row r="242">
@@ -3084,10 +3084,10 @@
         <v>46266.49930555555</v>
       </c>
       <c r="B242" t="n">
-        <v>97.5</v>
+        <v>97</v>
       </c>
       <c r="C242" t="n">
-        <v>447.1</v>
+        <v>403.7</v>
       </c>
     </row>
     <row r="243">
@@ -3095,10 +3095,10 @@
         <v>46266.5</v>
       </c>
       <c r="B243" t="n">
-        <v>94</v>
+        <v>99.2</v>
       </c>
       <c r="C243" t="n">
-        <v>429.6</v>
+        <v>401.9</v>
       </c>
     </row>
     <row r="244">
@@ -3106,10 +3106,10 @@
         <v>46266.50069444445</v>
       </c>
       <c r="B244" t="n">
-        <v>106.6</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C244" t="n">
-        <v>412.1</v>
+        <v>414.4</v>
       </c>
     </row>
     <row r="245">
@@ -3117,10 +3117,10 @@
         <v>46266.50138888889</v>
       </c>
       <c r="B245" t="n">
-        <v>103.9</v>
+        <v>102.9</v>
       </c>
       <c r="C245" t="n">
-        <v>415.1</v>
+        <v>448.9</v>
       </c>
     </row>
     <row r="246">
@@ -3128,10 +3128,10 @@
         <v>46266.50208333333</v>
       </c>
       <c r="B246" t="n">
-        <v>103.7</v>
+        <v>91.8</v>
       </c>
       <c r="C246" t="n">
-        <v>440.3</v>
+        <v>429.7</v>
       </c>
     </row>
     <row r="247">
@@ -3139,10 +3139,10 @@
         <v>46266.50277777778</v>
       </c>
       <c r="B247" t="n">
-        <v>105.9</v>
+        <v>97.7</v>
       </c>
       <c r="C247" t="n">
-        <v>428.3</v>
+        <v>429</v>
       </c>
     </row>
     <row r="248">
@@ -3150,10 +3150,10 @@
         <v>46266.50347222222</v>
       </c>
       <c r="B248" t="n">
-        <v>90.8</v>
+        <v>109.1</v>
       </c>
       <c r="C248" t="n">
-        <v>426.6</v>
+        <v>436.9</v>
       </c>
     </row>
     <row r="249">
@@ -3161,10 +3161,10 @@
         <v>46266.50416666667</v>
       </c>
       <c r="B249" t="n">
-        <v>103.2</v>
+        <v>90.8</v>
       </c>
       <c r="C249" t="n">
-        <v>403.4</v>
+        <v>445.5</v>
       </c>
     </row>
     <row r="250">
@@ -3172,10 +3172,10 @@
         <v>46266.50486111111</v>
       </c>
       <c r="B250" t="n">
-        <v>103</v>
+        <v>101.4</v>
       </c>
       <c r="C250" t="n">
-        <v>400.6</v>
+        <v>409.4</v>
       </c>
     </row>
     <row r="251">
@@ -3183,10 +3183,10 @@
         <v>46266.50555555556</v>
       </c>
       <c r="B251" t="n">
-        <v>98.40000000000001</v>
+        <v>102.1</v>
       </c>
       <c r="C251" t="n">
-        <v>424.5</v>
+        <v>425.1</v>
       </c>
     </row>
     <row r="252">
@@ -3194,10 +3194,10 @@
         <v>46266.50625</v>
       </c>
       <c r="B252" t="n">
-        <v>98.7</v>
+        <v>109.2</v>
       </c>
       <c r="C252" t="n">
-        <v>418.1</v>
+        <v>422.5</v>
       </c>
     </row>
     <row r="253">
@@ -3208,7 +3208,7 @@
         <v>152.5</v>
       </c>
       <c r="C253" t="n">
-        <v>444.6</v>
+        <v>440.5</v>
       </c>
     </row>
     <row r="254">
@@ -3216,10 +3216,10 @@
         <v>46266.50763888889</v>
       </c>
       <c r="B254" t="n">
-        <v>99.2</v>
+        <v>106.7</v>
       </c>
       <c r="C254" t="n">
-        <v>407.6</v>
+        <v>449.1</v>
       </c>
     </row>
     <row r="255">
@@ -3227,10 +3227,10 @@
         <v>46266.50833333333</v>
       </c>
       <c r="B255" t="n">
-        <v>93.5</v>
+        <v>91.7</v>
       </c>
       <c r="C255" t="n">
-        <v>426.1</v>
+        <v>432.3</v>
       </c>
     </row>
     <row r="256">
@@ -3238,10 +3238,10 @@
         <v>46266.50902777778</v>
       </c>
       <c r="B256" t="n">
-        <v>103</v>
+        <v>90.8</v>
       </c>
       <c r="C256" t="n">
-        <v>430.8</v>
+        <v>435.4</v>
       </c>
     </row>
     <row r="257">
@@ -3249,10 +3249,10 @@
         <v>46266.50972222222</v>
       </c>
       <c r="B257" t="n">
-        <v>108.4</v>
+        <v>109.8</v>
       </c>
       <c r="C257" t="n">
-        <v>438.7</v>
+        <v>426.2</v>
       </c>
     </row>
     <row r="258">
@@ -3260,10 +3260,10 @@
         <v>46266.51041666666</v>
       </c>
       <c r="B258" t="n">
-        <v>99.3</v>
+        <v>102.2</v>
       </c>
       <c r="C258" t="n">
-        <v>441.3</v>
+        <v>418.2</v>
       </c>
     </row>
     <row r="259">
@@ -3271,10 +3271,10 @@
         <v>46266.51111111111</v>
       </c>
       <c r="B259" t="n">
-        <v>101.8</v>
+        <v>108.4</v>
       </c>
       <c r="C259" t="n">
-        <v>416.1</v>
+        <v>419.4</v>
       </c>
     </row>
     <row r="260">
@@ -3282,10 +3282,10 @@
         <v>46266.51180555556</v>
       </c>
       <c r="B260" t="n">
-        <v>94.90000000000001</v>
+        <v>105.5</v>
       </c>
       <c r="C260" t="n">
-        <v>446.7</v>
+        <v>433.9</v>
       </c>
     </row>
     <row r="261">
@@ -3293,10 +3293,10 @@
         <v>46266.5125</v>
       </c>
       <c r="B261" t="n">
-        <v>95.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="C261" t="n">
-        <v>422.5</v>
+        <v>431.5</v>
       </c>
     </row>
     <row r="262">
@@ -3304,10 +3304,10 @@
         <v>46266.51319444444</v>
       </c>
       <c r="B262" t="n">
-        <v>105</v>
+        <v>96.7</v>
       </c>
       <c r="C262" t="n">
-        <v>428.5</v>
+        <v>416.5</v>
       </c>
     </row>
     <row r="263">
@@ -3315,10 +3315,10 @@
         <v>46266.51388888889</v>
       </c>
       <c r="B263" t="n">
-        <v>103.4</v>
+        <v>101.2</v>
       </c>
       <c r="C263" t="n">
-        <v>416.8</v>
+        <v>419.3</v>
       </c>
     </row>
     <row r="264">
@@ -3326,10 +3326,10 @@
         <v>46266.51458333333</v>
       </c>
       <c r="B264" t="n">
-        <v>99.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="C264" t="n">
-        <v>416.3</v>
+        <v>442.6</v>
       </c>
     </row>
     <row r="265">
@@ -3337,10 +3337,10 @@
         <v>46266.51527777778</v>
       </c>
       <c r="B265" t="n">
-        <v>99.8</v>
+        <v>109.3</v>
       </c>
       <c r="C265" t="n">
-        <v>417.7</v>
+        <v>430.1</v>
       </c>
     </row>
     <row r="266">
@@ -3348,10 +3348,10 @@
         <v>46266.51597222222</v>
       </c>
       <c r="B266" t="n">
-        <v>95.2</v>
+        <v>93</v>
       </c>
       <c r="C266" t="n">
-        <v>414</v>
+        <v>404.1</v>
       </c>
     </row>
     <row r="267">
@@ -3359,10 +3359,10 @@
         <v>46266.51666666667</v>
       </c>
       <c r="B267" t="n">
-        <v>101.9</v>
+        <v>103.3</v>
       </c>
       <c r="C267" t="n">
-        <v>444</v>
+        <v>445.8</v>
       </c>
     </row>
     <row r="268">
@@ -3370,10 +3370,10 @@
         <v>46266.51736111111</v>
       </c>
       <c r="B268" t="n">
-        <v>101.1</v>
+        <v>96.2</v>
       </c>
       <c r="C268" t="n">
-        <v>425.8</v>
+        <v>432.8</v>
       </c>
     </row>
     <row r="269">
@@ -3381,10 +3381,10 @@
         <v>46266.51805555556</v>
       </c>
       <c r="B269" t="n">
-        <v>93.8</v>
+        <v>103.2</v>
       </c>
       <c r="C269" t="n">
-        <v>412.1</v>
+        <v>406.4</v>
       </c>
     </row>
     <row r="270">
@@ -3392,10 +3392,10 @@
         <v>46266.51875</v>
       </c>
       <c r="B270" t="n">
-        <v>98.09999999999999</v>
+        <v>104.2</v>
       </c>
       <c r="C270" t="n">
-        <v>427.8</v>
+        <v>404.2</v>
       </c>
     </row>
     <row r="271">
@@ -3403,10 +3403,10 @@
         <v>46266.51944444444</v>
       </c>
       <c r="B271" t="n">
-        <v>94.8</v>
+        <v>101.2</v>
       </c>
       <c r="C271" t="n">
-        <v>423.8</v>
+        <v>432.2</v>
       </c>
     </row>
     <row r="272">
@@ -3414,10 +3414,10 @@
         <v>46266.52013888889</v>
       </c>
       <c r="B272" t="n">
-        <v>104.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="C272" t="n">
-        <v>422.4</v>
+        <v>406.4</v>
       </c>
     </row>
     <row r="273">
@@ -3425,10 +3425,10 @@
         <v>46266.52083333334</v>
       </c>
       <c r="B273" t="n">
-        <v>90.3</v>
+        <v>104.1</v>
       </c>
       <c r="C273" t="n">
-        <v>414.7</v>
+        <v>447.4</v>
       </c>
     </row>
     <row r="274">
@@ -3436,10 +3436,10 @@
         <v>46266.52152777778</v>
       </c>
       <c r="B274" t="n">
-        <v>98.09999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="C274" t="n">
-        <v>412.2</v>
+        <v>445.6</v>
       </c>
     </row>
     <row r="275">
@@ -3447,10 +3447,10 @@
         <v>46266.52222222222</v>
       </c>
       <c r="B275" t="n">
-        <v>103.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="C275" t="n">
-        <v>418.5</v>
+        <v>433.5</v>
       </c>
     </row>
     <row r="276">
@@ -3458,10 +3458,10 @@
         <v>46266.52291666667</v>
       </c>
       <c r="B276" t="n">
-        <v>101.1</v>
+        <v>100.2</v>
       </c>
       <c r="C276" t="n">
-        <v>417.2</v>
+        <v>400.9</v>
       </c>
     </row>
     <row r="277">
@@ -3469,10 +3469,10 @@
         <v>46266.52361111111</v>
       </c>
       <c r="B277" t="n">
-        <v>109.9</v>
+        <v>96.2</v>
       </c>
       <c r="C277" t="n">
-        <v>427.5</v>
+        <v>447.6</v>
       </c>
     </row>
     <row r="278">
@@ -3480,10 +3480,10 @@
         <v>46266.52430555555</v>
       </c>
       <c r="B278" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="C278" t="n">
-        <v>422.7</v>
+        <v>438.3</v>
       </c>
     </row>
     <row r="279">
@@ -3491,10 +3491,10 @@
         <v>46266.525</v>
       </c>
       <c r="B279" t="n">
-        <v>96.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="C279" t="n">
-        <v>411.5</v>
+        <v>450</v>
       </c>
     </row>
     <row r="280">
@@ -3502,10 +3502,10 @@
         <v>46266.52569444444</v>
       </c>
       <c r="B280" t="n">
-        <v>104.4</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="C280" t="n">
-        <v>415.8</v>
+        <v>414.8</v>
       </c>
     </row>
     <row r="281">
@@ -3513,10 +3513,10 @@
         <v>46266.52638888889</v>
       </c>
       <c r="B281" t="n">
-        <v>104.9</v>
+        <v>105.8</v>
       </c>
       <c r="C281" t="n">
-        <v>447.5</v>
+        <v>425.4</v>
       </c>
     </row>
     <row r="282">
@@ -3524,10 +3524,10 @@
         <v>46266.52708333333</v>
       </c>
       <c r="B282" t="n">
-        <v>103.8</v>
+        <v>100.8</v>
       </c>
       <c r="C282" t="n">
-        <v>409.6</v>
+        <v>436.9</v>
       </c>
     </row>
     <row r="283">
@@ -3535,10 +3535,10 @@
         <v>46266.52777777778</v>
       </c>
       <c r="B283" t="n">
-        <v>104.8</v>
+        <v>100.5</v>
       </c>
       <c r="C283" t="n">
-        <v>413.8</v>
+        <v>433.1</v>
       </c>
     </row>
     <row r="284">
@@ -3546,10 +3546,10 @@
         <v>46266.52847222222</v>
       </c>
       <c r="B284" t="n">
-        <v>101.8</v>
+        <v>107.5</v>
       </c>
       <c r="C284" t="n">
-        <v>438</v>
+        <v>430.9</v>
       </c>
     </row>
     <row r="285">
@@ -3560,7 +3560,7 @@
         <v>101.9</v>
       </c>
       <c r="C285" t="n">
-        <v>449</v>
+        <v>407.7</v>
       </c>
     </row>
     <row r="286">
@@ -3568,10 +3568,10 @@
         <v>46266.52986111111</v>
       </c>
       <c r="B286" t="n">
-        <v>106.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="C286" t="n">
-        <v>414.8</v>
+        <v>434.6</v>
       </c>
     </row>
     <row r="287">
@@ -3579,10 +3579,10 @@
         <v>46266.53055555555</v>
       </c>
       <c r="B287" t="n">
-        <v>97.2</v>
+        <v>102.5</v>
       </c>
       <c r="C287" t="n">
-        <v>415.1</v>
+        <v>445.1</v>
       </c>
     </row>
     <row r="288">
@@ -3590,10 +3590,10 @@
         <v>46266.53125</v>
       </c>
       <c r="B288" t="n">
-        <v>104.2</v>
+        <v>104.4</v>
       </c>
       <c r="C288" t="n">
-        <v>406.3</v>
+        <v>402.2</v>
       </c>
     </row>
     <row r="289">
@@ -3601,10 +3601,10 @@
         <v>46266.53194444445</v>
       </c>
       <c r="B289" t="n">
-        <v>90.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="C289" t="n">
-        <v>402.7</v>
+        <v>436</v>
       </c>
     </row>
     <row r="290">
@@ -3612,10 +3612,10 @@
         <v>46266.53263888889</v>
       </c>
       <c r="B290" t="n">
-        <v>95.8</v>
+        <v>109.4</v>
       </c>
       <c r="C290" t="n">
-        <v>447.2</v>
+        <v>430.5</v>
       </c>
     </row>
     <row r="291">
@@ -3623,10 +3623,10 @@
         <v>46266.53333333333</v>
       </c>
       <c r="B291" t="n">
-        <v>102.8</v>
+        <v>105</v>
       </c>
       <c r="C291" t="n">
-        <v>437.6</v>
+        <v>439.2</v>
       </c>
     </row>
     <row r="292">
@@ -3634,10 +3634,10 @@
         <v>46266.53402777778</v>
       </c>
       <c r="B292" t="n">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="C292" t="n">
-        <v>400.6</v>
+        <v>412</v>
       </c>
     </row>
     <row r="293">
@@ -3645,10 +3645,10 @@
         <v>46266.53472222222</v>
       </c>
       <c r="B293" t="n">
-        <v>95.7</v>
+        <v>109.3</v>
       </c>
       <c r="C293" t="n">
-        <v>423.9</v>
+        <v>439.2</v>
       </c>
     </row>
     <row r="294">
@@ -3656,10 +3656,10 @@
         <v>46266.53541666667</v>
       </c>
       <c r="B294" t="n">
-        <v>96.8</v>
+        <v>108.1</v>
       </c>
       <c r="C294" t="n">
-        <v>448.3</v>
+        <v>409.7</v>
       </c>
     </row>
     <row r="295">
@@ -3667,10 +3667,10 @@
         <v>46266.53611111111</v>
       </c>
       <c r="B295" t="n">
-        <v>95</v>
+        <v>103.6</v>
       </c>
       <c r="C295" t="n">
-        <v>443.1</v>
+        <v>428.5</v>
       </c>
     </row>
     <row r="296">
@@ -3678,10 +3678,10 @@
         <v>46266.53680555556</v>
       </c>
       <c r="B296" t="n">
-        <v>92.3</v>
+        <v>98.8</v>
       </c>
       <c r="C296" t="n">
-        <v>403.3</v>
+        <v>438.5</v>
       </c>
     </row>
     <row r="297">
@@ -3689,10 +3689,10 @@
         <v>46266.5375</v>
       </c>
       <c r="B297" t="n">
-        <v>99.8</v>
+        <v>105.6</v>
       </c>
       <c r="C297" t="n">
-        <v>428.9</v>
+        <v>425.1</v>
       </c>
     </row>
     <row r="298">
@@ -3700,10 +3700,10 @@
         <v>46266.53819444445</v>
       </c>
       <c r="B298" t="n">
-        <v>103.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="C298" t="n">
-        <v>407.6</v>
+        <v>408.1</v>
       </c>
     </row>
     <row r="299">
@@ -3711,10 +3711,10 @@
         <v>46266.53888888889</v>
       </c>
       <c r="B299" t="n">
-        <v>106.2</v>
+        <v>94</v>
       </c>
       <c r="C299" t="n">
-        <v>447.5</v>
+        <v>430.2</v>
       </c>
     </row>
     <row r="300">
@@ -3722,10 +3722,10 @@
         <v>46266.53958333333</v>
       </c>
       <c r="B300" t="n">
-        <v>91.7</v>
+        <v>107.5</v>
       </c>
       <c r="C300" t="n">
-        <v>412.4</v>
+        <v>402.6</v>
       </c>
     </row>
     <row r="301">
@@ -3733,10 +3733,10 @@
         <v>46266.54027777778</v>
       </c>
       <c r="B301" t="n">
-        <v>101.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C301" t="n">
-        <v>420.8</v>
+        <v>418.6</v>
       </c>
     </row>
     <row r="302">
@@ -3744,10 +3744,10 @@
         <v>46266.54097222222</v>
       </c>
       <c r="B302" t="n">
-        <v>101.9</v>
+        <v>108.7</v>
       </c>
       <c r="C302" t="n">
-        <v>430.9</v>
+        <v>435.6</v>
       </c>
     </row>
     <row r="303">
@@ -3755,7 +3755,7 @@
         <v>46266.54166666666</v>
       </c>
       <c r="B303" t="n">
-        <v>105.5</v>
+        <v>100.3</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>46266.54236111111</v>
       </c>
       <c r="B304" t="n">
-        <v>97.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="C304" t="n">
-        <v>445.4</v>
+        <v>404.2</v>
       </c>
     </row>
     <row r="305">
@@ -3779,10 +3779,10 @@
         <v>46266.54305555556</v>
       </c>
       <c r="B305" t="n">
-        <v>95.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C305" t="n">
-        <v>429.4</v>
+        <v>422.5</v>
       </c>
     </row>
     <row r="306">
@@ -3790,10 +3790,10 @@
         <v>46266.54375</v>
       </c>
       <c r="B306" t="n">
-        <v>98.59999999999999</v>
+        <v>100.3</v>
       </c>
       <c r="C306" t="n">
-        <v>428.4</v>
+        <v>441.6</v>
       </c>
     </row>
     <row r="307">
@@ -3801,10 +3801,10 @@
         <v>46266.54444444444</v>
       </c>
       <c r="B307" t="n">
-        <v>91.2</v>
+        <v>91.8</v>
       </c>
       <c r="C307" t="n">
-        <v>448</v>
+        <v>445.5</v>
       </c>
     </row>
     <row r="308">
@@ -3812,10 +3812,10 @@
         <v>46266.54513888889</v>
       </c>
       <c r="B308" t="n">
-        <v>92</v>
+        <v>106.3</v>
       </c>
       <c r="C308" t="n">
-        <v>438.1</v>
+        <v>444.2</v>
       </c>
     </row>
     <row r="309">
@@ -3823,10 +3823,10 @@
         <v>46266.54583333333</v>
       </c>
       <c r="B309" t="n">
-        <v>102.5</v>
+        <v>108.6</v>
       </c>
       <c r="C309" t="n">
-        <v>413.2</v>
+        <v>420.7</v>
       </c>
     </row>
     <row r="310">
@@ -3834,10 +3834,10 @@
         <v>46266.54652777778</v>
       </c>
       <c r="B310" t="n">
-        <v>91.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C310" t="n">
-        <v>412</v>
+        <v>418.7</v>
       </c>
     </row>
     <row r="311">
@@ -3845,10 +3845,10 @@
         <v>46266.54722222222</v>
       </c>
       <c r="B311" t="n">
-        <v>101</v>
+        <v>97.7</v>
       </c>
       <c r="C311" t="n">
-        <v>407.8</v>
+        <v>404.1</v>
       </c>
     </row>
     <row r="312">
@@ -3856,10 +3856,10 @@
         <v>46266.54791666667</v>
       </c>
       <c r="B312" t="n">
-        <v>98.2</v>
+        <v>94.5</v>
       </c>
       <c r="C312" t="n">
-        <v>434.5</v>
+        <v>415.9</v>
       </c>
     </row>
     <row r="313">
@@ -3867,10 +3867,10 @@
         <v>46266.54861111111</v>
       </c>
       <c r="B313" t="n">
-        <v>99.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="C313" t="n">
-        <v>401.6</v>
+        <v>435.7</v>
       </c>
     </row>
     <row r="314">
@@ -3878,10 +3878,10 @@
         <v>46266.54930555556</v>
       </c>
       <c r="B314" t="n">
-        <v>95.8</v>
+        <v>96.7</v>
       </c>
       <c r="C314" t="n">
-        <v>414.1</v>
+        <v>407.3</v>
       </c>
     </row>
     <row r="315">
@@ -3889,10 +3889,10 @@
         <v>46266.55</v>
       </c>
       <c r="B315" t="n">
-        <v>107.2</v>
+        <v>90.8</v>
       </c>
       <c r="C315" t="n">
-        <v>403.6</v>
+        <v>445.9</v>
       </c>
     </row>
     <row r="316">
@@ -3900,10 +3900,10 @@
         <v>46266.55069444444</v>
       </c>
       <c r="B316" t="n">
-        <v>94.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C316" t="n">
-        <v>413.2</v>
+        <v>441.6</v>
       </c>
     </row>
     <row r="317">
@@ -3911,10 +3911,10 @@
         <v>46266.55138888889</v>
       </c>
       <c r="B317" t="n">
-        <v>105.8</v>
+        <v>105.2</v>
       </c>
       <c r="C317" t="n">
-        <v>429.5</v>
+        <v>423.5</v>
       </c>
     </row>
     <row r="318">
@@ -3922,10 +3922,10 @@
         <v>46266.55208333334</v>
       </c>
       <c r="B318" t="n">
-        <v>106.1</v>
+        <v>102.3</v>
       </c>
       <c r="C318" t="n">
-        <v>409.9</v>
+        <v>445.3</v>
       </c>
     </row>
     <row r="319">
@@ -3933,10 +3933,10 @@
         <v>46266.55277777778</v>
       </c>
       <c r="B319" t="n">
-        <v>92.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="C319" t="n">
-        <v>411.2</v>
+        <v>410.8</v>
       </c>
     </row>
     <row r="320">
@@ -3947,7 +3947,7 @@
         <v>93</v>
       </c>
       <c r="C320" t="n">
-        <v>413.3</v>
+        <v>447</v>
       </c>
     </row>
     <row r="321">
@@ -3955,10 +3955,10 @@
         <v>46266.55416666667</v>
       </c>
       <c r="B321" t="n">
-        <v>92.8</v>
+        <v>102.2</v>
       </c>
       <c r="C321" t="n">
-        <v>403</v>
+        <v>421.2</v>
       </c>
     </row>
     <row r="322">
@@ -3966,10 +3966,10 @@
         <v>46266.55486111111</v>
       </c>
       <c r="B322" t="n">
-        <v>105.9</v>
+        <v>105.5</v>
       </c>
       <c r="C322" t="n">
-        <v>429.8</v>
+        <v>411.9</v>
       </c>
     </row>
     <row r="323">
@@ -3977,10 +3977,10 @@
         <v>46266.55555555555</v>
       </c>
       <c r="B323" t="n">
-        <v>106.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="C323" t="n">
-        <v>446.1</v>
+        <v>411.9</v>
       </c>
     </row>
     <row r="324">
@@ -3988,10 +3988,10 @@
         <v>46266.55625</v>
       </c>
       <c r="B324" t="n">
-        <v>98.8</v>
+        <v>102.8</v>
       </c>
       <c r="C324" t="n">
-        <v>423.4</v>
+        <v>431.1</v>
       </c>
     </row>
     <row r="325">
@@ -3999,10 +3999,10 @@
         <v>46266.55694444444</v>
       </c>
       <c r="B325" t="n">
-        <v>96.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="C325" t="n">
-        <v>420.1</v>
+        <v>441.8</v>
       </c>
     </row>
     <row r="326">
@@ -4010,10 +4010,10 @@
         <v>46266.55763888889</v>
       </c>
       <c r="B326" t="n">
-        <v>95.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="C326" t="n">
-        <v>427</v>
+        <v>426.8</v>
       </c>
     </row>
     <row r="327">
@@ -4021,10 +4021,10 @@
         <v>46266.55833333333</v>
       </c>
       <c r="B327" t="n">
-        <v>98.8</v>
+        <v>102.6</v>
       </c>
       <c r="C327" t="n">
-        <v>429.9</v>
+        <v>428.8</v>
       </c>
     </row>
     <row r="328">
@@ -4032,10 +4032,10 @@
         <v>46266.55902777778</v>
       </c>
       <c r="B328" t="n">
-        <v>107.8</v>
+        <v>104.4</v>
       </c>
       <c r="C328" t="n">
-        <v>436.7</v>
+        <v>414.6</v>
       </c>
     </row>
     <row r="329">
@@ -4043,10 +4043,10 @@
         <v>46266.55972222222</v>
       </c>
       <c r="B329" t="n">
-        <v>102.1</v>
+        <v>90</v>
       </c>
       <c r="C329" t="n">
-        <v>401.3</v>
+        <v>417.6</v>
       </c>
     </row>
     <row r="330">
@@ -4054,10 +4054,10 @@
         <v>46266.56041666667</v>
       </c>
       <c r="B330" t="n">
-        <v>94.59999999999999</v>
+        <v>101.4</v>
       </c>
       <c r="C330" t="n">
-        <v>433.7</v>
+        <v>409.4</v>
       </c>
     </row>
     <row r="331">
@@ -4065,10 +4065,10 @@
         <v>46266.56111111111</v>
       </c>
       <c r="B331" t="n">
-        <v>107.2</v>
+        <v>103.4</v>
       </c>
       <c r="C331" t="n">
-        <v>429.4</v>
+        <v>426.2</v>
       </c>
     </row>
     <row r="332">
@@ -4076,10 +4076,10 @@
         <v>46266.56180555555</v>
       </c>
       <c r="B332" t="n">
-        <v>90.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="C332" t="n">
-        <v>438.2</v>
+        <v>447.7</v>
       </c>
     </row>
     <row r="333">
@@ -4087,10 +4087,10 @@
         <v>46266.5625</v>
       </c>
       <c r="B333" t="n">
-        <v>106.4</v>
+        <v>100.9</v>
       </c>
       <c r="C333" t="n">
-        <v>428.8</v>
+        <v>439.3</v>
       </c>
     </row>
     <row r="334">
@@ -4098,10 +4098,10 @@
         <v>46266.56319444445</v>
       </c>
       <c r="B334" t="n">
-        <v>105.3</v>
+        <v>100.2</v>
       </c>
       <c r="C334" t="n">
-        <v>408.8</v>
+        <v>401</v>
       </c>
     </row>
     <row r="335">
@@ -4109,10 +4109,10 @@
         <v>46266.56388888889</v>
       </c>
       <c r="B335" t="n">
-        <v>100.4</v>
+        <v>107.5</v>
       </c>
       <c r="C335" t="n">
-        <v>422.1</v>
+        <v>402.2</v>
       </c>
     </row>
     <row r="336">
@@ -4120,10 +4120,10 @@
         <v>46266.56458333333</v>
       </c>
       <c r="B336" t="n">
-        <v>95.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="C336" t="n">
-        <v>449.8</v>
+        <v>418.7</v>
       </c>
     </row>
     <row r="337">
@@ -4131,10 +4131,10 @@
         <v>46266.56527777778</v>
       </c>
       <c r="B337" t="n">
-        <v>98.7</v>
+        <v>104.9</v>
       </c>
       <c r="C337" t="n">
-        <v>440.7</v>
+        <v>417.9</v>
       </c>
     </row>
     <row r="338">
@@ -4142,10 +4142,10 @@
         <v>46266.56597222222</v>
       </c>
       <c r="B338" t="n">
-        <v>109.4</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="C338" t="n">
-        <v>423.5</v>
+        <v>412.1</v>
       </c>
     </row>
     <row r="339">
@@ -4153,10 +4153,10 @@
         <v>46266.56666666667</v>
       </c>
       <c r="B339" t="n">
-        <v>98.2</v>
+        <v>103.1</v>
       </c>
       <c r="C339" t="n">
-        <v>416.1</v>
+        <v>405.2</v>
       </c>
     </row>
     <row r="340">
@@ -4164,10 +4164,10 @@
         <v>46266.56736111111</v>
       </c>
       <c r="B340" t="n">
-        <v>92.09999999999999</v>
+        <v>101.6</v>
       </c>
       <c r="C340" t="n">
-        <v>408</v>
+        <v>437.8</v>
       </c>
     </row>
     <row r="341">
@@ -4175,10 +4175,10 @@
         <v>46266.56805555556</v>
       </c>
       <c r="B341" t="n">
-        <v>98.2</v>
+        <v>92.7</v>
       </c>
       <c r="C341" t="n">
-        <v>424.8</v>
+        <v>417.6</v>
       </c>
     </row>
     <row r="342">
@@ -4186,10 +4186,10 @@
         <v>46266.56875</v>
       </c>
       <c r="B342" t="n">
-        <v>103.3</v>
+        <v>96.8</v>
       </c>
       <c r="C342" t="n">
-        <v>420</v>
+        <v>432.1</v>
       </c>
     </row>
     <row r="343">
@@ -4197,10 +4197,10 @@
         <v>46266.56944444445</v>
       </c>
       <c r="B343" t="n">
-        <v>105.2</v>
+        <v>106.6</v>
       </c>
       <c r="C343" t="n">
-        <v>401.8</v>
+        <v>434.2</v>
       </c>
     </row>
     <row r="344">
@@ -4208,10 +4208,10 @@
         <v>46266.57013888889</v>
       </c>
       <c r="B344" t="n">
-        <v>91.8</v>
+        <v>109.6</v>
       </c>
       <c r="C344" t="n">
-        <v>412.6</v>
+        <v>423.9</v>
       </c>
     </row>
     <row r="345">
@@ -4219,10 +4219,10 @@
         <v>46266.57083333333</v>
       </c>
       <c r="B345" t="n">
-        <v>92.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="C345" t="n">
-        <v>438.6</v>
+        <v>406.7</v>
       </c>
     </row>
     <row r="346">
@@ -4230,10 +4230,10 @@
         <v>46266.57152777778</v>
       </c>
       <c r="B346" t="n">
-        <v>107.3</v>
+        <v>104.3</v>
       </c>
       <c r="C346" t="n">
-        <v>441.2</v>
+        <v>447.2</v>
       </c>
     </row>
     <row r="347">
@@ -4241,10 +4241,10 @@
         <v>46266.57222222222</v>
       </c>
       <c r="B347" t="n">
-        <v>90</v>
+        <v>90.7</v>
       </c>
       <c r="C347" t="n">
-        <v>443.5</v>
+        <v>410.1</v>
       </c>
     </row>
     <row r="348">
@@ -4252,10 +4252,10 @@
         <v>46266.57291666666</v>
       </c>
       <c r="B348" t="n">
-        <v>99.2</v>
+        <v>105.8</v>
       </c>
       <c r="C348" t="n">
-        <v>402.7</v>
+        <v>444.3</v>
       </c>
     </row>
     <row r="349">
@@ -4263,10 +4263,10 @@
         <v>46266.57361111111</v>
       </c>
       <c r="B349" t="n">
-        <v>100.4</v>
+        <v>96.3</v>
       </c>
       <c r="C349" t="n">
-        <v>431.1</v>
+        <v>415.5</v>
       </c>
     </row>
     <row r="350">
@@ -4274,10 +4274,10 @@
         <v>46266.57430555556</v>
       </c>
       <c r="B350" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C350" t="n">
-        <v>422.1</v>
+        <v>440.8</v>
       </c>
     </row>
     <row r="351">
@@ -4285,10 +4285,10 @@
         <v>46266.575</v>
       </c>
       <c r="B351" t="n">
-        <v>91</v>
+        <v>99.5</v>
       </c>
       <c r="C351" t="n">
-        <v>413.4</v>
+        <v>401.8</v>
       </c>
     </row>
     <row r="352">
@@ -4296,10 +4296,10 @@
         <v>46266.57569444444</v>
       </c>
       <c r="B352" t="n">
-        <v>92.59999999999999</v>
+        <v>102.9</v>
       </c>
       <c r="C352" t="n">
-        <v>414.4</v>
+        <v>414.3</v>
       </c>
     </row>
     <row r="353">
@@ -4307,10 +4307,10 @@
         <v>46266.57638888889</v>
       </c>
       <c r="B353" t="n">
-        <v>107.6</v>
+        <v>107.2</v>
       </c>
       <c r="C353" t="n">
-        <v>424.2</v>
+        <v>402.4</v>
       </c>
     </row>
     <row r="354">
@@ -4318,10 +4318,10 @@
         <v>46266.57708333333</v>
       </c>
       <c r="B354" t="n">
-        <v>90.59999999999999</v>
+        <v>103.1</v>
       </c>
       <c r="C354" t="n">
-        <v>431.5</v>
+        <v>413.7</v>
       </c>
     </row>
     <row r="355">
@@ -4332,7 +4332,7 @@
         <v>106</v>
       </c>
       <c r="C355" t="n">
-        <v>435.5</v>
+        <v>421.8</v>
       </c>
     </row>
     <row r="356">
@@ -4340,10 +4340,10 @@
         <v>46266.57847222222</v>
       </c>
       <c r="B356" t="n">
-        <v>96.2</v>
+        <v>98</v>
       </c>
       <c r="C356" t="n">
-        <v>400.7</v>
+        <v>422</v>
       </c>
     </row>
     <row r="357">
@@ -4351,10 +4351,10 @@
         <v>46266.57916666667</v>
       </c>
       <c r="B357" t="n">
-        <v>98.2</v>
+        <v>109.1</v>
       </c>
       <c r="C357" t="n">
-        <v>411.2</v>
+        <v>417</v>
       </c>
     </row>
     <row r="358">
@@ -4362,10 +4362,10 @@
         <v>46266.57986111111</v>
       </c>
       <c r="B358" t="n">
-        <v>106.8</v>
+        <v>93.7</v>
       </c>
       <c r="C358" t="n">
-        <v>405.7</v>
+        <v>434.6</v>
       </c>
     </row>
     <row r="359">
@@ -4373,10 +4373,10 @@
         <v>46266.58055555556</v>
       </c>
       <c r="B359" t="n">
-        <v>108.9</v>
+        <v>97.3</v>
       </c>
       <c r="C359" t="n">
-        <v>432.4</v>
+        <v>439.9</v>
       </c>
     </row>
     <row r="360">
@@ -4384,10 +4384,10 @@
         <v>46266.58125</v>
       </c>
       <c r="B360" t="n">
-        <v>93.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="C360" t="n">
-        <v>446.6</v>
+        <v>404.1</v>
       </c>
     </row>
     <row r="361">
@@ -4395,10 +4395,10 @@
         <v>46266.58194444444</v>
       </c>
       <c r="B361" t="n">
-        <v>95.8</v>
+        <v>98.5</v>
       </c>
       <c r="C361" t="n">
-        <v>435.3</v>
+        <v>421.5</v>
       </c>
     </row>
     <row r="362">
@@ -4406,10 +4406,10 @@
         <v>46266.58263888889</v>
       </c>
       <c r="B362" t="n">
-        <v>98.3</v>
+        <v>109.9</v>
       </c>
       <c r="C362" t="n">
-        <v>424.1</v>
+        <v>409</v>
       </c>
     </row>
     <row r="363">
@@ -4417,10 +4417,10 @@
         <v>46266.58333333334</v>
       </c>
       <c r="B363" t="n">
-        <v>99.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C363" t="n">
-        <v>422.8</v>
+        <v>405.1</v>
       </c>
     </row>
     <row r="364">
@@ -4428,10 +4428,10 @@
         <v>46266.58402777778</v>
       </c>
       <c r="B364" t="n">
-        <v>92.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="C364" t="n">
-        <v>409.5</v>
+        <v>414.8</v>
       </c>
     </row>
     <row r="365">
@@ -4439,10 +4439,10 @@
         <v>46266.58472222222</v>
       </c>
       <c r="B365" t="n">
-        <v>102</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C365" t="n">
-        <v>437.3</v>
+        <v>435.9</v>
       </c>
     </row>
     <row r="366">
@@ -4450,10 +4450,10 @@
         <v>46266.58541666667</v>
       </c>
       <c r="B366" t="n">
-        <v>92.7</v>
+        <v>93.3</v>
       </c>
       <c r="C366" t="n">
-        <v>403.5</v>
+        <v>422.2</v>
       </c>
     </row>
     <row r="367">
@@ -4461,10 +4461,10 @@
         <v>46266.58611111111</v>
       </c>
       <c r="B367" t="n">
-        <v>105.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C367" t="n">
-        <v>442.7</v>
+        <v>436.3</v>
       </c>
     </row>
     <row r="368">
@@ -4472,10 +4472,10 @@
         <v>46266.58680555555</v>
       </c>
       <c r="B368" t="n">
-        <v>96.8</v>
+        <v>108.2</v>
       </c>
       <c r="C368" t="n">
-        <v>439.4</v>
+        <v>430.7</v>
       </c>
     </row>
     <row r="369">
@@ -4483,10 +4483,10 @@
         <v>46266.5875</v>
       </c>
       <c r="B369" t="n">
-        <v>95.3</v>
+        <v>98.7</v>
       </c>
       <c r="C369" t="n">
-        <v>400.1</v>
+        <v>432</v>
       </c>
     </row>
     <row r="370">
@@ -4494,10 +4494,10 @@
         <v>46266.58819444444</v>
       </c>
       <c r="B370" t="n">
-        <v>104.5</v>
+        <v>105.8</v>
       </c>
       <c r="C370" t="n">
-        <v>441.9</v>
+        <v>402.9</v>
       </c>
     </row>
     <row r="371">
@@ -4505,10 +4505,10 @@
         <v>46266.58888888889</v>
       </c>
       <c r="B371" t="n">
-        <v>101.6</v>
+        <v>103.4</v>
       </c>
       <c r="C371" t="n">
-        <v>433</v>
+        <v>420.3</v>
       </c>
     </row>
     <row r="372">
@@ -4516,10 +4516,10 @@
         <v>46266.58958333333</v>
       </c>
       <c r="B372" t="n">
-        <v>107.3</v>
+        <v>100.3</v>
       </c>
       <c r="C372" t="n">
-        <v>422.3</v>
+        <v>437.5</v>
       </c>
     </row>
     <row r="373">
@@ -4527,10 +4527,10 @@
         <v>46266.59027777778</v>
       </c>
       <c r="B373" t="n">
-        <v>99.7</v>
+        <v>93.2</v>
       </c>
       <c r="C373" t="n">
-        <v>416.6</v>
+        <v>401.6</v>
       </c>
     </row>
     <row r="374">
@@ -4538,10 +4538,10 @@
         <v>46266.59097222222</v>
       </c>
       <c r="B374" t="n">
-        <v>105.3</v>
+        <v>107</v>
       </c>
       <c r="C374" t="n">
-        <v>418.9</v>
+        <v>433.9</v>
       </c>
     </row>
     <row r="375">
@@ -4549,10 +4549,10 @@
         <v>46266.59166666667</v>
       </c>
       <c r="B375" t="n">
-        <v>108.7</v>
+        <v>98.8</v>
       </c>
       <c r="C375" t="n">
-        <v>443.5</v>
+        <v>406.3</v>
       </c>
     </row>
     <row r="376">
@@ -4560,10 +4560,10 @@
         <v>46266.59236111111</v>
       </c>
       <c r="B376" t="n">
-        <v>109.6</v>
+        <v>94.7</v>
       </c>
       <c r="C376" t="n">
-        <v>411.9</v>
+        <v>432.3</v>
       </c>
     </row>
     <row r="377">
@@ -4571,10 +4571,10 @@
         <v>46266.59305555555</v>
       </c>
       <c r="B377" t="n">
-        <v>97.7</v>
+        <v>97.2</v>
       </c>
       <c r="C377" t="n">
-        <v>442.8</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="378">
@@ -4582,10 +4582,10 @@
         <v>46266.59375</v>
       </c>
       <c r="B378" t="n">
-        <v>98.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="C378" t="n">
-        <v>415.9</v>
+        <v>407.7</v>
       </c>
     </row>
     <row r="379">
@@ -4593,10 +4593,10 @@
         <v>46266.59444444445</v>
       </c>
       <c r="B379" t="n">
-        <v>99.5</v>
+        <v>99</v>
       </c>
       <c r="C379" t="n">
-        <v>445.7</v>
+        <v>418.5</v>
       </c>
     </row>
     <row r="380">
@@ -4604,10 +4604,10 @@
         <v>46266.59513888889</v>
       </c>
       <c r="B380" t="n">
-        <v>97.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C380" t="n">
-        <v>449.4</v>
+        <v>403.8</v>
       </c>
     </row>
     <row r="381">
@@ -4615,10 +4615,10 @@
         <v>46266.59583333333</v>
       </c>
       <c r="B381" t="n">
-        <v>105.8</v>
+        <v>92.8</v>
       </c>
       <c r="C381" t="n">
-        <v>432.6</v>
+        <v>418.3</v>
       </c>
     </row>
     <row r="382">
@@ -4626,10 +4626,10 @@
         <v>46266.59652777778</v>
       </c>
       <c r="B382" t="n">
-        <v>93</v>
+        <v>96.3</v>
       </c>
       <c r="C382" t="n">
-        <v>448.2</v>
+        <v>413.9</v>
       </c>
     </row>
     <row r="383">
@@ -4637,10 +4637,10 @@
         <v>46266.59722222222</v>
       </c>
       <c r="B383" t="n">
-        <v>92.5</v>
+        <v>109.2</v>
       </c>
       <c r="C383" t="n">
-        <v>448.3</v>
+        <v>401.3</v>
       </c>
     </row>
     <row r="384">
@@ -4648,10 +4648,10 @@
         <v>46266.59791666667</v>
       </c>
       <c r="B384" t="n">
-        <v>96.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="C384" t="n">
-        <v>405</v>
+        <v>425.9</v>
       </c>
     </row>
     <row r="385">
@@ -4659,10 +4659,10 @@
         <v>46266.59861111111</v>
       </c>
       <c r="B385" t="n">
-        <v>106.9</v>
+        <v>108.3</v>
       </c>
       <c r="C385" t="n">
-        <v>405</v>
+        <v>405.9</v>
       </c>
     </row>
     <row r="386">
@@ -4670,10 +4670,10 @@
         <v>46266.59930555556</v>
       </c>
       <c r="B386" t="n">
-        <v>108.2</v>
+        <v>105.5</v>
       </c>
       <c r="C386" t="n">
-        <v>400.8</v>
+        <v>435.2</v>
       </c>
     </row>
     <row r="387">
@@ -4681,10 +4681,10 @@
         <v>46266.6</v>
       </c>
       <c r="B387" t="n">
-        <v>92.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="C387" t="n">
-        <v>443.5</v>
+        <v>430.6</v>
       </c>
     </row>
     <row r="388">
@@ -4692,10 +4692,10 @@
         <v>46266.60069444445</v>
       </c>
       <c r="B388" t="n">
-        <v>109.4</v>
+        <v>103.9</v>
       </c>
       <c r="C388" t="n">
-        <v>403.7</v>
+        <v>449.9</v>
       </c>
     </row>
     <row r="389">
@@ -4703,10 +4703,10 @@
         <v>46266.60138888889</v>
       </c>
       <c r="B389" t="n">
-        <v>105.6</v>
+        <v>94</v>
       </c>
       <c r="C389" t="n">
-        <v>413.3</v>
+        <v>406.8</v>
       </c>
     </row>
     <row r="390">
@@ -4714,10 +4714,10 @@
         <v>46266.60208333333</v>
       </c>
       <c r="B390" t="n">
-        <v>102.5</v>
+        <v>91.5</v>
       </c>
       <c r="C390" t="n">
-        <v>419.9</v>
+        <v>408.6</v>
       </c>
     </row>
     <row r="391">
@@ -4725,10 +4725,10 @@
         <v>46266.60277777778</v>
       </c>
       <c r="B391" t="n">
-        <v>91.59999999999999</v>
+        <v>104.3</v>
       </c>
       <c r="C391" t="n">
-        <v>416.4</v>
+        <v>449.9</v>
       </c>
     </row>
     <row r="392">
@@ -4736,10 +4736,10 @@
         <v>46266.60347222222</v>
       </c>
       <c r="B392" t="n">
-        <v>103.5</v>
+        <v>106.2</v>
       </c>
       <c r="C392" t="n">
-        <v>426.7</v>
+        <v>448.4</v>
       </c>
     </row>
     <row r="393">
@@ -4747,10 +4747,10 @@
         <v>46266.60416666666</v>
       </c>
       <c r="B393" t="n">
-        <v>109.1</v>
+        <v>109.7</v>
       </c>
       <c r="C393" t="n">
-        <v>431.3</v>
+        <v>433.4</v>
       </c>
     </row>
     <row r="394">
@@ -4758,10 +4758,10 @@
         <v>46266.60486111111</v>
       </c>
       <c r="B394" t="n">
-        <v>107.7</v>
+        <v>104.2</v>
       </c>
       <c r="C394" t="n">
-        <v>424.4</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="395">
@@ -4769,10 +4769,10 @@
         <v>46266.60555555556</v>
       </c>
       <c r="B395" t="n">
-        <v>100.8</v>
+        <v>95.8</v>
       </c>
       <c r="C395" t="n">
-        <v>430.9</v>
+        <v>415</v>
       </c>
     </row>
     <row r="396">
@@ -4780,10 +4780,10 @@
         <v>46266.60625</v>
       </c>
       <c r="B396" t="n">
-        <v>94.7</v>
+        <v>93.2</v>
       </c>
       <c r="C396" t="n">
-        <v>434.2</v>
+        <v>435.5</v>
       </c>
     </row>
     <row r="397">
@@ -4791,10 +4791,10 @@
         <v>46266.60694444444</v>
       </c>
       <c r="B397" t="n">
-        <v>95.7</v>
+        <v>104</v>
       </c>
       <c r="C397" t="n">
-        <v>411.4</v>
+        <v>408.7</v>
       </c>
     </row>
     <row r="398">
@@ -4802,10 +4802,10 @@
         <v>46266.60763888889</v>
       </c>
       <c r="B398" t="n">
-        <v>91.8</v>
+        <v>97.2</v>
       </c>
       <c r="C398" t="n">
-        <v>448.9</v>
+        <v>411.2</v>
       </c>
     </row>
     <row r="399">
@@ -4813,10 +4813,10 @@
         <v>46266.60833333333</v>
       </c>
       <c r="B399" t="n">
-        <v>105.2</v>
+        <v>109.7</v>
       </c>
       <c r="C399" t="n">
-        <v>435.2</v>
+        <v>439.6</v>
       </c>
     </row>
     <row r="400">
@@ -4824,10 +4824,10 @@
         <v>46266.60902777778</v>
       </c>
       <c r="B400" t="n">
-        <v>92</v>
+        <v>94.7</v>
       </c>
       <c r="C400" t="n">
-        <v>408.3</v>
+        <v>424.7</v>
       </c>
     </row>
     <row r="401">
@@ -4835,10 +4835,10 @@
         <v>46266.60972222222</v>
       </c>
       <c r="B401" t="n">
-        <v>96</v>
+        <v>97.2</v>
       </c>
       <c r="C401" t="n">
-        <v>401.4</v>
+        <v>428.6</v>
       </c>
     </row>
     <row r="402">
@@ -4846,10 +4846,10 @@
         <v>46266.61041666667</v>
       </c>
       <c r="B402" t="n">
-        <v>96.5</v>
+        <v>99.3</v>
       </c>
       <c r="C402" t="n">
-        <v>402.8</v>
+        <v>449.2</v>
       </c>
     </row>
   </sheetData>
